--- a/LTL_qty_updated_7.28.26.xlsx
+++ b/LTL_qty_updated_7.28.26.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acusa-my.sharepoint.com/personal/g_ghedini_atlasconcordeusa_com/Documents/Desktop/AI - Automations/BOL creation/SAP_cleaning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6160EAF0-1319-425F-818F-4192C3B46458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{6160EAF0-1319-425F-818F-4192C3B46458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A679F11A-D80B-4578-8C3B-069CD43A4790}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B388D9E8-F042-4987-BDB7-8E3EC1CFA04A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B388D9E8-F042-4987-BDB7-8E3EC1CFA04A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$164</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="277">
   <si>
     <t>D23_Floor and Wall Tiles</t>
   </si>
@@ -1756,7 +1756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F30446A3-A986-4686-A765-4C12AB9F4FB1}">
-  <dimension ref="A1:G287"/>
+  <dimension ref="A1:G288"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
@@ -2801,16 +2801,19 @@
         <v>29</v>
       </c>
       <c r="B47" s="8">
-        <v>610010004574</v>
+        <v>600010000908</v>
       </c>
       <c r="C47" t="s">
-        <v>121</v>
+        <v>64</v>
+      </c>
+      <c r="D47">
+        <v>5</v>
       </c>
       <c r="E47">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F47">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G47" t="s">
         <v>151</v>
@@ -2820,20 +2823,17 @@
       <c r="A48" t="s">
         <v>29</v>
       </c>
-      <c r="B48" s="2">
-        <v>610010005520</v>
+      <c r="B48" s="8">
+        <v>610010004574</v>
       </c>
       <c r="C48" t="s">
-        <v>18</v>
-      </c>
-      <c r="D48">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="E48">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F48">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="G48" t="s">
         <v>151</v>
@@ -2844,19 +2844,19 @@
         <v>29</v>
       </c>
       <c r="B49" s="2">
-        <v>610010005394</v>
-      </c>
-      <c r="C49" s="13" t="s">
+        <v>610010005520</v>
+      </c>
+      <c r="C49" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49">
         <v>19</v>
       </c>
-      <c r="D49">
-        <v>5</v>
-      </c>
       <c r="E49">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F49">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="G49" t="s">
         <v>151</v>
@@ -2866,17 +2866,20 @@
       <c r="A50" t="s">
         <v>29</v>
       </c>
-      <c r="B50" s="8">
-        <v>610010004573</v>
-      </c>
-      <c r="C50" t="s">
-        <v>122</v>
+      <c r="B50" s="2">
+        <v>610010005394</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50">
+        <v>5</v>
       </c>
       <c r="E50">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F50">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="G50" t="s">
         <v>151</v>
@@ -2887,7 +2890,7 @@
         <v>29</v>
       </c>
       <c r="B51" s="8">
-        <v>610010005473</v>
+        <v>610010004573</v>
       </c>
       <c r="C51" t="s">
         <v>122</v>
@@ -2907,19 +2910,16 @@
         <v>29</v>
       </c>
       <c r="B52" s="8">
-        <v>610010001040</v>
+        <v>610010005473</v>
       </c>
       <c r="C52" t="s">
-        <v>65</v>
-      </c>
-      <c r="D52">
-        <v>5</v>
+        <v>122</v>
       </c>
       <c r="E52">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F52">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G52" t="s">
         <v>151</v>
@@ -2930,16 +2930,19 @@
         <v>29</v>
       </c>
       <c r="B53" s="8">
-        <v>610010004572</v>
+        <v>610010001040</v>
       </c>
       <c r="C53" t="s">
-        <v>123</v>
+        <v>65</v>
+      </c>
+      <c r="D53">
+        <v>5</v>
       </c>
       <c r="E53">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F53">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G53" t="s">
         <v>151</v>
@@ -2950,19 +2953,16 @@
         <v>29</v>
       </c>
       <c r="B54" s="8">
-        <v>610010001043</v>
+        <v>610010004572</v>
       </c>
       <c r="C54" t="s">
-        <v>66</v>
-      </c>
-      <c r="D54">
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="E54">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F54">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G54" t="s">
         <v>151</v>
@@ -2973,16 +2973,19 @@
         <v>29</v>
       </c>
       <c r="B55" s="8">
-        <v>610010004575</v>
+        <v>610010001043</v>
       </c>
       <c r="C55" t="s">
-        <v>124</v>
+        <v>66</v>
+      </c>
+      <c r="D55">
+        <v>5</v>
       </c>
       <c r="E55">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F55">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G55" t="s">
         <v>151</v>
@@ -2993,19 +2996,16 @@
         <v>29</v>
       </c>
       <c r="B56" s="8">
-        <v>610010001039</v>
+        <v>610010004575</v>
       </c>
       <c r="C56" t="s">
-        <v>67</v>
-      </c>
-      <c r="D56">
-        <v>5</v>
+        <v>124</v>
       </c>
       <c r="E56">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F56">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G56" t="s">
         <v>151</v>
@@ -3016,16 +3016,19 @@
         <v>29</v>
       </c>
       <c r="B57" s="8">
-        <v>610010004571</v>
-      </c>
-      <c r="C57" s="12" t="s">
-        <v>125</v>
+        <v>610010001039</v>
+      </c>
+      <c r="C57" t="s">
+        <v>67</v>
+      </c>
+      <c r="D57">
+        <v>5</v>
       </c>
       <c r="E57">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F57">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G57" t="s">
         <v>151</v>
@@ -3036,19 +3039,16 @@
         <v>29</v>
       </c>
       <c r="B58" s="8">
-        <v>610010005313</v>
-      </c>
-      <c r="C58" t="s">
-        <v>68</v>
-      </c>
-      <c r="D58">
-        <v>19</v>
+        <v>610010004571</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>125</v>
       </c>
       <c r="E58">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F58">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="G58" t="s">
         <v>151</v>
@@ -3059,19 +3059,19 @@
         <v>29</v>
       </c>
       <c r="B59" s="8">
-        <v>610010005274</v>
+        <v>610010005313</v>
       </c>
       <c r="C59" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D59">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E59">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F59">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="G59" t="s">
         <v>151</v>
@@ -3082,16 +3082,19 @@
         <v>29</v>
       </c>
       <c r="B60" s="8">
-        <v>610010005283</v>
+        <v>610010005274</v>
       </c>
       <c r="C60" t="s">
-        <v>126</v>
+        <v>69</v>
+      </c>
+      <c r="D60">
+        <v>5</v>
       </c>
       <c r="E60">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F60">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G60" t="s">
         <v>151</v>
@@ -3102,19 +3105,16 @@
         <v>29</v>
       </c>
       <c r="B61" s="8">
-        <v>610010005319</v>
+        <v>610010005283</v>
       </c>
       <c r="C61" t="s">
-        <v>70</v>
-      </c>
-      <c r="D61">
-        <v>19</v>
+        <v>126</v>
       </c>
       <c r="E61">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F61">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="G61" t="s">
         <v>151</v>
@@ -3125,19 +3125,19 @@
         <v>29</v>
       </c>
       <c r="B62" s="8">
-        <v>610010005280</v>
+        <v>610010005319</v>
       </c>
       <c r="C62" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D62">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E62">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F62">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="G62" t="s">
         <v>151</v>
@@ -3148,16 +3148,19 @@
         <v>29</v>
       </c>
       <c r="B63" s="8">
-        <v>610010005289</v>
+        <v>610010005280</v>
       </c>
       <c r="C63" t="s">
-        <v>127</v>
+        <v>71</v>
+      </c>
+      <c r="D63">
+        <v>5</v>
       </c>
       <c r="E63">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F63">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G63" t="s">
         <v>151</v>
@@ -3168,19 +3171,16 @@
         <v>29</v>
       </c>
       <c r="B64" s="8">
-        <v>610010005317</v>
+        <v>610010005289</v>
       </c>
       <c r="C64" t="s">
-        <v>72</v>
-      </c>
-      <c r="D64">
-        <v>19</v>
+        <v>127</v>
       </c>
       <c r="E64">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F64">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="G64" t="s">
         <v>151</v>
@@ -3191,19 +3191,19 @@
         <v>29</v>
       </c>
       <c r="B65" s="8">
-        <v>610010005278</v>
+        <v>610010005317</v>
       </c>
       <c r="C65" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D65">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E65">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F65">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="G65" t="s">
         <v>151</v>
@@ -3214,16 +3214,19 @@
         <v>29</v>
       </c>
       <c r="B66" s="8">
-        <v>610010005287</v>
+        <v>610010005278</v>
       </c>
       <c r="C66" t="s">
-        <v>128</v>
+        <v>73</v>
+      </c>
+      <c r="D66">
+        <v>5</v>
       </c>
       <c r="E66">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F66">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G66" t="s">
         <v>151</v>
@@ -3234,19 +3237,16 @@
         <v>29</v>
       </c>
       <c r="B67" s="8">
-        <v>610010005318</v>
+        <v>610010005287</v>
       </c>
       <c r="C67" t="s">
-        <v>74</v>
-      </c>
-      <c r="D67">
-        <v>19</v>
+        <v>128</v>
       </c>
       <c r="E67">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F67">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="G67" t="s">
         <v>151</v>
@@ -3257,19 +3257,19 @@
         <v>29</v>
       </c>
       <c r="B68" s="8">
-        <v>610010005279</v>
+        <v>610010005318</v>
       </c>
       <c r="C68" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E68">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F68">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="G68" t="s">
         <v>151</v>
@@ -3280,16 +3280,19 @@
         <v>29</v>
       </c>
       <c r="B69" s="8">
-        <v>610010005288</v>
+        <v>610010005279</v>
       </c>
       <c r="C69" t="s">
-        <v>129</v>
+        <v>75</v>
+      </c>
+      <c r="D69">
+        <v>5</v>
       </c>
       <c r="E69">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F69">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G69" t="s">
         <v>151</v>
@@ -3300,19 +3303,16 @@
         <v>29</v>
       </c>
       <c r="B70" s="8">
-        <v>610010005314</v>
+        <v>610010005288</v>
       </c>
       <c r="C70" t="s">
-        <v>76</v>
-      </c>
-      <c r="D70">
-        <v>19</v>
+        <v>129</v>
       </c>
       <c r="E70">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F70">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="G70" t="s">
         <v>151</v>
@@ -3323,19 +3323,19 @@
         <v>29</v>
       </c>
       <c r="B71" s="8">
-        <v>610010005275</v>
+        <v>610010005314</v>
       </c>
       <c r="C71" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D71">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E71">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F71">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="G71" t="s">
         <v>151</v>
@@ -3346,16 +3346,19 @@
         <v>29</v>
       </c>
       <c r="B72" s="8">
-        <v>610010005284</v>
+        <v>610010005275</v>
       </c>
       <c r="C72" t="s">
-        <v>130</v>
+        <v>77</v>
+      </c>
+      <c r="D72">
+        <v>5</v>
       </c>
       <c r="E72">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F72">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G72" t="s">
         <v>151</v>
@@ -3365,20 +3368,17 @@
       <c r="A73" t="s">
         <v>29</v>
       </c>
-      <c r="B73" s="2">
-        <v>610130007000</v>
-      </c>
-      <c r="C73" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D73">
-        <v>15</v>
+      <c r="B73" s="8">
+        <v>610010005284</v>
+      </c>
+      <c r="C73" t="s">
+        <v>130</v>
       </c>
       <c r="E73">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F73">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G73" t="s">
         <v>151</v>
@@ -3389,10 +3389,10 @@
         <v>29</v>
       </c>
       <c r="B74" s="2">
-        <v>610130000920</v>
+        <v>610130007000</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D74">
         <v>15</v>
@@ -3412,10 +3412,10 @@
         <v>29</v>
       </c>
       <c r="B75" s="2">
-        <v>610130007215</v>
+        <v>610130000920</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D75">
         <v>15</v>
@@ -3435,10 +3435,10 @@
         <v>29</v>
       </c>
       <c r="B76" s="2">
-        <v>610130007001</v>
+        <v>610130007215</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D76">
         <v>15</v>
@@ -3458,10 +3458,10 @@
         <v>29</v>
       </c>
       <c r="B77" s="2">
-        <v>610130000919</v>
+        <v>610130007001</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D77">
         <v>15</v>
@@ -3481,19 +3481,19 @@
         <v>29</v>
       </c>
       <c r="B78" s="2">
-        <v>610010002391</v>
-      </c>
-      <c r="C78" t="s">
-        <v>78</v>
+        <v>610130000919</v>
+      </c>
+      <c r="C78" s="14" t="s">
+        <v>26</v>
       </c>
       <c r="D78">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E78">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F78">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="G78" t="s">
         <v>151</v>
@@ -3504,10 +3504,10 @@
         <v>29</v>
       </c>
       <c r="B79" s="2">
-        <v>610010002393</v>
+        <v>610010002391</v>
       </c>
       <c r="C79" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D79">
         <v>6</v>
@@ -3527,10 +3527,10 @@
         <v>29</v>
       </c>
       <c r="B80" s="2">
-        <v>610010002392</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>80</v>
+        <v>610010002393</v>
+      </c>
+      <c r="C80" t="s">
+        <v>79</v>
       </c>
       <c r="D80">
         <v>6</v>
@@ -3550,19 +3550,19 @@
         <v>29</v>
       </c>
       <c r="B81" s="2">
-        <v>610010004527</v>
-      </c>
-      <c r="C81" t="s">
-        <v>81</v>
+        <v>610010002392</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="D81">
         <v>6</v>
       </c>
       <c r="E81">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F81">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="G81" t="s">
         <v>151</v>
@@ -3573,10 +3573,10 @@
         <v>29</v>
       </c>
       <c r="B82" s="2">
-        <v>610010004530</v>
+        <v>610010004527</v>
       </c>
       <c r="C82" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D82">
         <v>6</v>
@@ -3596,10 +3596,10 @@
         <v>29</v>
       </c>
       <c r="B83" s="2">
-        <v>610010004905</v>
+        <v>610010004530</v>
       </c>
       <c r="C83" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D83">
         <v>6</v>
@@ -3619,10 +3619,10 @@
         <v>29</v>
       </c>
       <c r="B84" s="2">
-        <v>610010002361</v>
+        <v>610010004905</v>
       </c>
       <c r="C84" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D84">
         <v>6</v>
@@ -3642,10 +3642,10 @@
         <v>29</v>
       </c>
       <c r="B85" s="2">
-        <v>610010004901</v>
+        <v>610010002361</v>
       </c>
       <c r="C85" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D85">
         <v>6</v>
@@ -3665,10 +3665,10 @@
         <v>29</v>
       </c>
       <c r="B86" s="2">
-        <v>610010004900</v>
+        <v>610010004901</v>
       </c>
       <c r="C86" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D86">
         <v>6</v>
@@ -3688,10 +3688,10 @@
         <v>29</v>
       </c>
       <c r="B87" s="2">
-        <v>610010004902</v>
-      </c>
-      <c r="C87" s="14" t="s">
-        <v>87</v>
+        <v>610010004900</v>
+      </c>
+      <c r="C87" t="s">
+        <v>86</v>
       </c>
       <c r="D87">
         <v>6</v>
@@ -3711,10 +3711,10 @@
         <v>29</v>
       </c>
       <c r="B88" s="2">
-        <v>610010004906</v>
+        <v>610010004902</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D88">
         <v>6</v>
@@ -3734,10 +3734,10 @@
         <v>29</v>
       </c>
       <c r="B89" s="2">
-        <v>610010002360</v>
+        <v>610010004906</v>
       </c>
       <c r="C89" s="14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D89">
         <v>6</v>
@@ -3756,11 +3756,11 @@
       <c r="A90" t="s">
         <v>29</v>
       </c>
-      <c r="B90" s="5">
-        <v>610010002851</v>
+      <c r="B90" s="2">
+        <v>610010002360</v>
       </c>
       <c r="C90" s="14" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="D90">
         <v>6</v>
@@ -3769,21 +3769,21 @@
         <v>29</v>
       </c>
       <c r="F90">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G90" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>29</v>
       </c>
-      <c r="B91" s="2">
-        <v>610010004582</v>
+      <c r="B91" s="5">
+        <v>610010002851</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="D91">
         <v>6</v>
@@ -3792,10 +3792,10 @@
         <v>29</v>
       </c>
       <c r="F91">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G91" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
@@ -3803,10 +3803,10 @@
         <v>29</v>
       </c>
       <c r="B92" s="2">
-        <v>610010004581</v>
-      </c>
-      <c r="C92" t="s">
-        <v>91</v>
+        <v>610010004582</v>
+      </c>
+      <c r="C92" s="14" t="s">
+        <v>90</v>
       </c>
       <c r="D92">
         <v>6</v>
@@ -3826,10 +3826,10 @@
         <v>29</v>
       </c>
       <c r="B93" s="2">
-        <v>610010004580</v>
+        <v>610010004581</v>
       </c>
       <c r="C93" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D93">
         <v>6</v>
@@ -3849,10 +3849,10 @@
         <v>29</v>
       </c>
       <c r="B94" s="2">
-        <v>610010004532</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>93</v>
+        <v>610010004580</v>
+      </c>
+      <c r="C94" t="s">
+        <v>92</v>
       </c>
       <c r="D94">
         <v>6</v>
@@ -3872,10 +3872,10 @@
         <v>29</v>
       </c>
       <c r="B95" s="2">
-        <v>610010002362</v>
-      </c>
-      <c r="C95" t="s">
-        <v>94</v>
+        <v>610010004532</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="D95">
         <v>6</v>
@@ -3895,10 +3895,10 @@
         <v>29</v>
       </c>
       <c r="B96" s="2">
-        <v>610010004903</v>
+        <v>610010002362</v>
       </c>
       <c r="C96" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D96">
         <v>6</v>
@@ -3918,10 +3918,10 @@
         <v>29</v>
       </c>
       <c r="B97" s="2">
-        <v>610010002814</v>
+        <v>610010004903</v>
       </c>
       <c r="C97" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D97">
         <v>6</v>
@@ -3941,10 +3941,10 @@
         <v>29</v>
       </c>
       <c r="B98" s="2">
-        <v>610010002816</v>
-      </c>
-      <c r="C98" s="14" t="s">
-        <v>97</v>
+        <v>610010002814</v>
+      </c>
+      <c r="C98" t="s">
+        <v>96</v>
       </c>
       <c r="D98">
         <v>6</v>
@@ -3964,10 +3964,10 @@
         <v>29</v>
       </c>
       <c r="B99" s="2">
-        <v>610010002815</v>
+        <v>610010002816</v>
       </c>
       <c r="C99" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D99">
         <v>6</v>
@@ -3987,10 +3987,10 @@
         <v>29</v>
       </c>
       <c r="B100" s="2">
-        <v>610010002817</v>
+        <v>610010002815</v>
       </c>
       <c r="C100" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D100">
         <v>6</v>
@@ -4010,16 +4010,16 @@
         <v>29</v>
       </c>
       <c r="B101" s="2">
-        <v>610110001402</v>
+        <v>610010002817</v>
       </c>
       <c r="C101" s="14" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="D101">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E101">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F101">
         <v>36</v>
@@ -4030,22 +4030,22 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B102" s="2">
-        <v>600010000961</v>
+        <v>610110001402</v>
       </c>
       <c r="C102" s="14" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D102">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F102">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="G102" t="s">
         <v>151</v>
@@ -4056,19 +4056,19 @@
         <v>30</v>
       </c>
       <c r="B103" s="2">
-        <v>610010004651</v>
-      </c>
-      <c r="C103" t="s">
-        <v>32</v>
+        <v>600010000961</v>
+      </c>
+      <c r="C103" s="14" t="s">
+        <v>31</v>
       </c>
       <c r="D103">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E103">
         <v>0</v>
       </c>
       <c r="F103">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G103" t="s">
         <v>151</v>
@@ -4079,19 +4079,19 @@
         <v>30</v>
       </c>
       <c r="B104" s="2">
-        <v>600010000962</v>
+        <v>610010004651</v>
       </c>
       <c r="C104" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="D104">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E104">
         <v>0</v>
       </c>
       <c r="F104">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G104" t="s">
         <v>151</v>
@@ -4102,19 +4102,19 @@
         <v>30</v>
       </c>
       <c r="B105" s="2">
-        <v>610010003151</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>51</v>
+        <v>600010000962</v>
+      </c>
+      <c r="C105" t="s">
+        <v>100</v>
       </c>
       <c r="D105">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E105">
         <v>0</v>
       </c>
       <c r="F105">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G105" t="s">
         <v>151</v>
@@ -4125,19 +4125,19 @@
         <v>30</v>
       </c>
       <c r="B106" s="2">
-        <v>610010005863</v>
-      </c>
-      <c r="C106" t="s">
-        <v>101</v>
+        <v>610010003151</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="D106">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E106">
         <v>0</v>
       </c>
       <c r="F106">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G106" t="s">
         <v>151</v>
@@ -4148,19 +4148,19 @@
         <v>30</v>
       </c>
       <c r="B107" s="2">
-        <v>610010002001</v>
+        <v>610010005863</v>
       </c>
       <c r="C107" t="s">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="D107">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E107">
         <v>0</v>
       </c>
       <c r="F107">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G107" t="s">
         <v>151</v>
@@ -4171,19 +4171,19 @@
         <v>30</v>
       </c>
       <c r="B108" s="2">
-        <v>610010004650</v>
+        <v>610010002001</v>
       </c>
       <c r="C108" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D108">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E108">
         <v>0</v>
       </c>
       <c r="F108">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G108" t="s">
         <v>151</v>
@@ -4194,10 +4194,10 @@
         <v>30</v>
       </c>
       <c r="B109" s="2">
-        <v>610010005864</v>
-      </c>
-      <c r="C109" s="14" t="s">
-        <v>102</v>
+        <v>610010004650</v>
+      </c>
+      <c r="C109" t="s">
+        <v>34</v>
       </c>
       <c r="D109">
         <v>4</v>
@@ -4217,19 +4217,19 @@
         <v>30</v>
       </c>
       <c r="B110" s="2">
-        <v>610010002206</v>
+        <v>610010005864</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="D110">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E110">
         <v>0</v>
       </c>
       <c r="F110">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G110" t="s">
         <v>151</v>
@@ -4240,10 +4240,10 @@
         <v>30</v>
       </c>
       <c r="B111" s="2">
-        <v>610010002317</v>
+        <v>610010002206</v>
       </c>
       <c r="C111" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D111">
         <v>7</v>
@@ -4263,19 +4263,19 @@
         <v>30</v>
       </c>
       <c r="B112" s="2">
-        <v>610010004653</v>
+        <v>610010002317</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D112">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E112">
         <v>0</v>
       </c>
       <c r="F112">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G112" t="s">
         <v>151</v>
@@ -4286,19 +4286,19 @@
         <v>30</v>
       </c>
       <c r="B113" s="2">
-        <v>610010005509</v>
+        <v>610010004653</v>
       </c>
       <c r="C113" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D113">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E113">
         <v>0</v>
       </c>
       <c r="F113">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G113" t="s">
         <v>151</v>
@@ -4309,19 +4309,19 @@
         <v>30</v>
       </c>
       <c r="B114" s="2">
-        <v>610010005527</v>
-      </c>
-      <c r="C114" t="s">
-        <v>103</v>
+        <v>610010005509</v>
+      </c>
+      <c r="C114" s="14" t="s">
+        <v>38</v>
       </c>
       <c r="D114">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E114">
         <v>0</v>
       </c>
       <c r="F114">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G114" t="s">
         <v>151</v>
@@ -4332,19 +4332,19 @@
         <v>30</v>
       </c>
       <c r="B115" s="2">
-        <v>610010002221</v>
+        <v>610010005527</v>
       </c>
       <c r="C115" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D115">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E115">
         <v>0</v>
       </c>
       <c r="F115">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G115" t="s">
         <v>151</v>
@@ -4355,10 +4355,10 @@
         <v>30</v>
       </c>
       <c r="B116" s="2">
-        <v>610010002315</v>
-      </c>
-      <c r="C116" s="3" t="s">
-        <v>105</v>
+        <v>610010002221</v>
+      </c>
+      <c r="C116" t="s">
+        <v>104</v>
       </c>
       <c r="D116">
         <v>7</v>
@@ -4378,19 +4378,19 @@
         <v>30</v>
       </c>
       <c r="B117" s="2">
-        <v>610010005660</v>
-      </c>
-      <c r="C117" t="s">
-        <v>106</v>
+        <v>610010002315</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="D117">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E117">
         <v>0</v>
       </c>
       <c r="F117">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G117" t="s">
         <v>151</v>
@@ -4401,10 +4401,10 @@
         <v>30</v>
       </c>
       <c r="B118" s="2">
-        <v>610010005788</v>
+        <v>610010005660</v>
       </c>
       <c r="C118" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D118">
         <v>4</v>
@@ -4424,10 +4424,10 @@
         <v>30</v>
       </c>
       <c r="B119" s="2">
-        <v>610010005661</v>
+        <v>610010005788</v>
       </c>
       <c r="C119" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D119">
         <v>4</v>
@@ -4447,19 +4447,19 @@
         <v>30</v>
       </c>
       <c r="B120" s="2">
-        <v>610010002220</v>
-      </c>
-      <c r="C120" s="14" t="s">
-        <v>39</v>
+        <v>610010005661</v>
+      </c>
+      <c r="C120" t="s">
+        <v>108</v>
       </c>
       <c r="D120">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E120">
         <v>0</v>
       </c>
       <c r="F120">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G120" t="s">
         <v>151</v>
@@ -4470,19 +4470,19 @@
         <v>30</v>
       </c>
       <c r="B121" s="2">
-        <v>610010004652</v>
+        <v>610010002220</v>
       </c>
       <c r="C121" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D121">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E121">
         <v>0</v>
       </c>
       <c r="F121">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G121" t="s">
         <v>151</v>
@@ -4493,19 +4493,19 @@
         <v>30</v>
       </c>
       <c r="B122" s="2">
-        <v>600010000959</v>
+        <v>610010004652</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D122">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E122">
         <v>0</v>
       </c>
       <c r="F122">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G122" t="s">
         <v>151</v>
@@ -4516,19 +4516,19 @@
         <v>30</v>
       </c>
       <c r="B123" s="2">
-        <v>610010005866</v>
+        <v>600010000959</v>
       </c>
       <c r="C123" s="14" t="s">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="D123">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E123">
         <v>0</v>
       </c>
       <c r="F123">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G123" t="s">
         <v>151</v>
@@ -4539,10 +4539,10 @@
         <v>30</v>
       </c>
       <c r="B124" s="2">
-        <v>610010005865</v>
+        <v>610010005866</v>
       </c>
       <c r="C124" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D124">
         <v>4</v>
@@ -4562,10 +4562,10 @@
         <v>30</v>
       </c>
       <c r="B125" s="2">
-        <v>610010005526</v>
-      </c>
-      <c r="C125" t="s">
-        <v>111</v>
+        <v>610010005865</v>
+      </c>
+      <c r="C125" s="14" t="s">
+        <v>110</v>
       </c>
       <c r="D125">
         <v>4</v>
@@ -4585,10 +4585,10 @@
         <v>30</v>
       </c>
       <c r="B126" s="2">
-        <v>610010005571</v>
+        <v>610010005526</v>
       </c>
       <c r="C126" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D126">
         <v>4</v>
@@ -4608,10 +4608,10 @@
         <v>30</v>
       </c>
       <c r="B127" s="2">
-        <v>610010005913</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>113</v>
+        <v>610010005571</v>
+      </c>
+      <c r="C127" t="s">
+        <v>112</v>
       </c>
       <c r="D127">
         <v>4</v>
@@ -4631,10 +4631,10 @@
         <v>30</v>
       </c>
       <c r="B128" s="2">
-        <v>610010005912</v>
-      </c>
-      <c r="C128" t="s">
-        <v>114</v>
+        <v>610010005913</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="D128">
         <v>4</v>
@@ -4654,10 +4654,10 @@
         <v>30</v>
       </c>
       <c r="B129" s="2">
-        <v>610010005570</v>
+        <v>610010005912</v>
       </c>
       <c r="C129" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D129">
         <v>4</v>
@@ -4677,10 +4677,10 @@
         <v>30</v>
       </c>
       <c r="B130" s="2">
-        <v>610010005525</v>
+        <v>610010005570</v>
       </c>
       <c r="C130" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D130">
         <v>4</v>
@@ -4697,19 +4697,22 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B131" s="2">
-        <v>610010006068</v>
-      </c>
-      <c r="C131" s="14" t="s">
-        <v>132</v>
+        <v>610010005525</v>
+      </c>
+      <c r="C131" t="s">
+        <v>116</v>
+      </c>
+      <c r="D131">
+        <v>4</v>
       </c>
       <c r="E131">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F131">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G131" t="s">
         <v>151</v>
@@ -4720,10 +4723,10 @@
         <v>29</v>
       </c>
       <c r="B132" s="2">
-        <v>610010006069</v>
+        <v>610010006068</v>
       </c>
       <c r="C132" s="14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E132">
         <v>2</v>
@@ -4740,19 +4743,16 @@
         <v>29</v>
       </c>
       <c r="B133" s="2">
-        <v>610010006070</v>
+        <v>610010006069</v>
       </c>
       <c r="C133" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="D133">
-        <v>5</v>
+        <v>133</v>
       </c>
       <c r="E133">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F133">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G133" t="s">
         <v>151</v>
@@ -4763,16 +4763,16 @@
         <v>29</v>
       </c>
       <c r="B134" s="2">
-        <v>610010005867</v>
+        <v>610010006070</v>
       </c>
       <c r="C134" s="14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D134">
         <v>5</v>
       </c>
       <c r="E134">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F134">
         <v>32</v>
@@ -4786,16 +4786,19 @@
         <v>29</v>
       </c>
       <c r="B135" s="2">
-        <v>610010006054</v>
+        <v>610010005867</v>
       </c>
       <c r="C135" s="14" t="s">
-        <v>136</v>
+        <v>135</v>
+      </c>
+      <c r="D135">
+        <v>5</v>
       </c>
       <c r="E135">
         <v>2</v>
       </c>
       <c r="F135">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G135" t="s">
         <v>151</v>
@@ -4806,19 +4809,16 @@
         <v>29</v>
       </c>
       <c r="B136" s="2">
-        <v>610010006097</v>
-      </c>
-      <c r="C136" t="s">
-        <v>137</v>
-      </c>
-      <c r="D136">
-        <v>5</v>
+        <v>610010006054</v>
+      </c>
+      <c r="C136" s="14" t="s">
+        <v>136</v>
       </c>
       <c r="E136">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F136">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G136" t="s">
         <v>151</v>
@@ -4829,10 +4829,10 @@
         <v>29</v>
       </c>
       <c r="B137" s="2">
-        <v>610010006098</v>
+        <v>610010006097</v>
       </c>
       <c r="C137" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D137">
         <v>5</v>
@@ -4852,16 +4852,16 @@
         <v>29</v>
       </c>
       <c r="B138" s="2">
-        <v>610010006073</v>
-      </c>
-      <c r="C138" s="3" t="s">
-        <v>139</v>
+        <v>610010006098</v>
+      </c>
+      <c r="C138" t="s">
+        <v>138</v>
       </c>
       <c r="D138">
         <v>5</v>
       </c>
       <c r="E138">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F138">
         <v>32</v>
@@ -4875,16 +4875,19 @@
         <v>29</v>
       </c>
       <c r="B139" s="2">
-        <v>610010005960</v>
-      </c>
-      <c r="C139" t="s">
-        <v>140</v>
+        <v>610010006073</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D139">
+        <v>5</v>
       </c>
       <c r="E139">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F139">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G139" t="s">
         <v>151</v>
@@ -4895,19 +4898,16 @@
         <v>29</v>
       </c>
       <c r="B140" s="2">
-        <v>610010004563</v>
+        <v>610010005960</v>
       </c>
       <c r="C140" t="s">
-        <v>141</v>
-      </c>
-      <c r="D140">
-        <v>5</v>
+        <v>140</v>
       </c>
       <c r="E140">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F140">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G140" t="s">
         <v>151</v>
@@ -4918,10 +4918,10 @@
         <v>29</v>
       </c>
       <c r="B141" s="2">
-        <v>610010004560</v>
+        <v>610010004563</v>
       </c>
       <c r="C141" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D141">
         <v>5</v>
@@ -4941,10 +4941,10 @@
         <v>29</v>
       </c>
       <c r="B142" s="2">
-        <v>610010004561</v>
-      </c>
-      <c r="C142" s="14" t="s">
-        <v>143</v>
+        <v>610010004560</v>
+      </c>
+      <c r="C142" t="s">
+        <v>142</v>
       </c>
       <c r="D142">
         <v>5</v>
@@ -4964,10 +4964,10 @@
         <v>29</v>
       </c>
       <c r="B143" s="2">
-        <v>610010004562</v>
+        <v>610010004561</v>
       </c>
       <c r="C143" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D143">
         <v>5</v>
@@ -4987,16 +4987,16 @@
         <v>29</v>
       </c>
       <c r="B144" s="2">
-        <v>610010006072</v>
+        <v>610010004562</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D144">
         <v>5</v>
       </c>
       <c r="E144">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F144">
         <v>32</v>
@@ -5010,19 +5010,22 @@
         <v>29</v>
       </c>
       <c r="B145" s="2">
-        <v>600010000897</v>
-      </c>
-      <c r="C145" t="s">
-        <v>146</v>
+        <v>610010006072</v>
+      </c>
+      <c r="C145" s="14" t="s">
+        <v>145</v>
       </c>
       <c r="D145">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="E145">
+        <v>8</v>
       </c>
       <c r="F145">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G145" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
@@ -5030,10 +5033,10 @@
         <v>29</v>
       </c>
       <c r="B146" s="2">
-        <v>600010009350</v>
+        <v>600010000897</v>
       </c>
       <c r="C146" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D146">
         <v>6</v>
@@ -5050,10 +5053,10 @@
         <v>29</v>
       </c>
       <c r="B147" s="2">
-        <v>600010009351</v>
+        <v>600010009350</v>
       </c>
       <c r="C147" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D147">
         <v>6</v>
@@ -5070,22 +5073,19 @@
         <v>29</v>
       </c>
       <c r="B148" s="2">
-        <v>610010006071</v>
+        <v>600010009351</v>
       </c>
       <c r="C148" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D148">
-        <v>5</v>
-      </c>
-      <c r="E148">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F148">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G148" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
@@ -5093,16 +5093,19 @@
         <v>29</v>
       </c>
       <c r="B149" s="2">
-        <v>610010006101</v>
+        <v>610010006071</v>
       </c>
       <c r="C149" t="s">
-        <v>153</v>
+        <v>152</v>
+      </c>
+      <c r="D149">
+        <v>5</v>
       </c>
       <c r="E149">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F149">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G149" t="s">
         <v>151</v>
@@ -5113,19 +5116,16 @@
         <v>29</v>
       </c>
       <c r="B150" s="2">
-        <v>610010005779</v>
+        <v>610010006101</v>
       </c>
       <c r="C150" t="s">
-        <v>154</v>
-      </c>
-      <c r="D150">
-        <v>5</v>
+        <v>153</v>
       </c>
       <c r="E150">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F150">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G150" t="s">
         <v>151</v>
@@ -5136,10 +5136,10 @@
         <v>29</v>
       </c>
       <c r="B151" s="2">
-        <v>610010005781</v>
+        <v>610010005779</v>
       </c>
       <c r="C151" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D151">
         <v>5</v>
@@ -5159,19 +5159,19 @@
         <v>29</v>
       </c>
       <c r="B152" s="2">
-        <v>610110001491</v>
+        <v>610010005781</v>
       </c>
       <c r="C152" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D152">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E152">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F152">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G152" t="s">
         <v>151</v>
@@ -5182,19 +5182,19 @@
         <v>29</v>
       </c>
       <c r="B153" s="2">
-        <v>610010005273</v>
+        <v>610110001491</v>
       </c>
       <c r="C153" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D153">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E153">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F153">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G153" t="s">
         <v>151</v>
@@ -5205,10 +5205,10 @@
         <v>29</v>
       </c>
       <c r="B154" s="2">
-        <v>610010005276</v>
+        <v>610010005273</v>
       </c>
       <c r="C154" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D154">
         <v>5</v>
@@ -5228,10 +5228,10 @@
         <v>29</v>
       </c>
       <c r="B155" s="2">
-        <v>610010005277</v>
+        <v>610010005276</v>
       </c>
       <c r="C155" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D155">
         <v>5</v>
@@ -5251,10 +5251,10 @@
         <v>29</v>
       </c>
       <c r="B156" s="2">
-        <v>610010005269</v>
+        <v>610010005277</v>
       </c>
       <c r="C156" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D156">
         <v>5</v>
@@ -5274,10 +5274,10 @@
         <v>29</v>
       </c>
       <c r="B157" s="2">
-        <v>610010005267</v>
+        <v>610010005269</v>
       </c>
       <c r="C157" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D157">
         <v>5</v>
@@ -5297,19 +5297,19 @@
         <v>29</v>
       </c>
       <c r="B158" s="2">
-        <v>610110000995</v>
+        <v>610010005267</v>
       </c>
       <c r="C158" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D158">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E158">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F158">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G158" t="s">
         <v>151</v>
@@ -5320,10 +5320,10 @@
         <v>29</v>
       </c>
       <c r="B159" s="2">
-        <v>610110001007</v>
+        <v>610110000995</v>
       </c>
       <c r="C159" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D159">
         <v>7</v>
@@ -5343,10 +5343,10 @@
         <v>29</v>
       </c>
       <c r="B160" s="2">
-        <v>610110001008</v>
+        <v>610110001007</v>
       </c>
       <c r="C160" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D160">
         <v>7</v>
@@ -5363,22 +5363,22 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B161" s="2">
-        <v>610010005930</v>
+        <v>610110001008</v>
       </c>
       <c r="C161" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D161">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E161">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F161">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="G161" t="s">
         <v>151</v>
@@ -5389,10 +5389,10 @@
         <v>30</v>
       </c>
       <c r="B162" s="2">
-        <v>610010005931</v>
+        <v>610010005930</v>
       </c>
       <c r="C162" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D162">
         <v>4</v>
@@ -5412,10 +5412,10 @@
         <v>30</v>
       </c>
       <c r="B163" s="2">
-        <v>610010006327</v>
+        <v>610010005931</v>
       </c>
       <c r="C163" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D163">
         <v>4</v>
@@ -5432,22 +5432,22 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B164" s="2">
-        <v>610010005598</v>
+        <v>610010006327</v>
       </c>
       <c r="C164" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D164">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E164">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F164">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G164" t="s">
         <v>151</v>
@@ -5458,10 +5458,10 @@
         <v>29</v>
       </c>
       <c r="B165" s="2">
-        <v>610010005600</v>
+        <v>610010005598</v>
       </c>
       <c r="C165" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D165">
         <v>5</v>
@@ -5481,10 +5481,10 @@
         <v>29</v>
       </c>
       <c r="B166" s="2">
-        <v>610010005599</v>
+        <v>610010005600</v>
       </c>
       <c r="C166" t="s">
-        <v>218</v>
+        <v>170</v>
       </c>
       <c r="D166">
         <v>5</v>
@@ -5504,10 +5504,10 @@
         <v>29</v>
       </c>
       <c r="B167" s="2">
-        <v>610010005601</v>
+        <v>610010005599</v>
       </c>
       <c r="C167" t="s">
-        <v>171</v>
+        <v>218</v>
       </c>
       <c r="D167">
         <v>5</v>
@@ -5527,10 +5527,10 @@
         <v>29</v>
       </c>
       <c r="B168" s="2">
-        <v>610010005656</v>
+        <v>610010005601</v>
       </c>
       <c r="C168" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D168">
         <v>5</v>
@@ -5550,10 +5550,10 @@
         <v>29</v>
       </c>
       <c r="B169" s="2">
-        <v>610010005658</v>
+        <v>610010005656</v>
       </c>
       <c r="C169" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D169">
         <v>5</v>
@@ -5573,10 +5573,10 @@
         <v>29</v>
       </c>
       <c r="B170" s="2">
-        <v>610010005657</v>
+        <v>610010005658</v>
       </c>
       <c r="C170" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D170">
         <v>5</v>
@@ -5596,10 +5596,10 @@
         <v>29</v>
       </c>
       <c r="B171" s="2">
-        <v>610010005659</v>
+        <v>610010005657</v>
       </c>
       <c r="C171" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D171">
         <v>5</v>
@@ -5619,10 +5619,10 @@
         <v>29</v>
       </c>
       <c r="B172" s="2">
-        <v>610010004674</v>
+        <v>610010005659</v>
       </c>
       <c r="C172" t="s">
-        <v>224</v>
+        <v>171</v>
       </c>
       <c r="D172">
         <v>5</v>
@@ -5642,10 +5642,10 @@
         <v>29</v>
       </c>
       <c r="B173" s="2">
-        <v>610010002255</v>
+        <v>610010004674</v>
       </c>
       <c r="C173" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D173">
         <v>5</v>
@@ -5665,10 +5665,10 @@
         <v>29</v>
       </c>
       <c r="B174" s="2">
-        <v>610010004677</v>
+        <v>610010002255</v>
       </c>
       <c r="C174" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D174">
         <v>5</v>
@@ -5688,10 +5688,10 @@
         <v>29</v>
       </c>
       <c r="B175" s="2">
-        <v>610010004676</v>
+        <v>610010004677</v>
       </c>
       <c r="C175" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D175">
         <v>5</v>
@@ -5711,10 +5711,10 @@
         <v>29</v>
       </c>
       <c r="B176" s="2">
-        <v>610010004673</v>
+        <v>610010004676</v>
       </c>
       <c r="C176" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D176">
         <v>5</v>
@@ -5734,10 +5734,10 @@
         <v>29</v>
       </c>
       <c r="B177" s="2">
-        <v>610010002258</v>
+        <v>610010004673</v>
       </c>
       <c r="C177" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D177">
         <v>5</v>
@@ -5757,10 +5757,10 @@
         <v>29</v>
       </c>
       <c r="B178" s="2">
-        <v>610010002256</v>
+        <v>610010002258</v>
       </c>
       <c r="C178" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D178">
         <v>5</v>
@@ -5780,10 +5780,10 @@
         <v>29</v>
       </c>
       <c r="B179" s="2">
-        <v>610010002254</v>
+        <v>610010002256</v>
       </c>
       <c r="C179" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D179">
         <v>5</v>
@@ -5803,10 +5803,10 @@
         <v>29</v>
       </c>
       <c r="B180" s="2">
-        <v>610010004675</v>
+        <v>610010002254</v>
       </c>
       <c r="C180" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D180">
         <v>5</v>
@@ -5826,10 +5826,10 @@
         <v>29</v>
       </c>
       <c r="B181" s="2">
-        <v>610010002257</v>
+        <v>610010004675</v>
       </c>
       <c r="C181" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D181">
         <v>5</v>
@@ -5849,10 +5849,10 @@
         <v>29</v>
       </c>
       <c r="B182" s="2">
-        <v>610010005776</v>
+        <v>610010002257</v>
       </c>
       <c r="C182" t="s">
-        <v>173</v>
+        <v>233</v>
       </c>
       <c r="D182">
         <v>5</v>
@@ -5872,10 +5872,10 @@
         <v>29</v>
       </c>
       <c r="B183" s="2">
-        <v>610010005773</v>
+        <v>610010005776</v>
       </c>
       <c r="C183" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D183">
         <v>5</v>
@@ -5895,10 +5895,10 @@
         <v>29</v>
       </c>
       <c r="B184" s="2">
-        <v>610010005774</v>
+        <v>610010005773</v>
       </c>
       <c r="C184" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D184">
         <v>5</v>
@@ -5918,10 +5918,10 @@
         <v>29</v>
       </c>
       <c r="B185" s="2">
-        <v>610010005772</v>
+        <v>610010005774</v>
       </c>
       <c r="C185" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D185">
         <v>5</v>
@@ -5941,10 +5941,10 @@
         <v>29</v>
       </c>
       <c r="B186" s="2">
-        <v>610010005775</v>
+        <v>610010005772</v>
       </c>
       <c r="C186" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D186">
         <v>5</v>
@@ -5964,10 +5964,10 @@
         <v>29</v>
       </c>
       <c r="B187" s="2">
-        <v>610010005771</v>
+        <v>610010005775</v>
       </c>
       <c r="C187" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D187">
         <v>5</v>
@@ -5987,19 +5987,19 @@
         <v>29</v>
       </c>
       <c r="B188" s="2">
-        <v>610010005878</v>
+        <v>610010005771</v>
       </c>
       <c r="C188" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D188">
         <v>5</v>
       </c>
       <c r="E188">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F188">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G188" t="s">
         <v>151</v>
@@ -6010,10 +6010,10 @@
         <v>29</v>
       </c>
       <c r="B189" s="2">
-        <v>610010005875</v>
+        <v>610010005878</v>
       </c>
       <c r="C189" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D189">
         <v>5</v>
@@ -6033,10 +6033,10 @@
         <v>29</v>
       </c>
       <c r="B190" s="2">
-        <v>610010005876</v>
+        <v>610010005875</v>
       </c>
       <c r="C190" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D190">
         <v>5</v>
@@ -6056,10 +6056,10 @@
         <v>29</v>
       </c>
       <c r="B191" s="2">
-        <v>610010005874</v>
+        <v>610010005876</v>
       </c>
       <c r="C191" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D191">
         <v>5</v>
@@ -6079,10 +6079,10 @@
         <v>29</v>
       </c>
       <c r="B192" s="2">
-        <v>610010005877</v>
+        <v>610010005874</v>
       </c>
       <c r="C192" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D192">
         <v>5</v>
@@ -6102,10 +6102,10 @@
         <v>29</v>
       </c>
       <c r="B193" s="2">
-        <v>610010005873</v>
+        <v>610010005877</v>
       </c>
       <c r="C193" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D193">
         <v>5</v>
@@ -6125,19 +6125,19 @@
         <v>29</v>
       </c>
       <c r="B194" s="2">
-        <v>610010005593</v>
+        <v>610010005873</v>
       </c>
       <c r="C194" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D194">
         <v>5</v>
       </c>
       <c r="E194">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F194">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G194" t="s">
         <v>151</v>
@@ -6148,10 +6148,10 @@
         <v>29</v>
       </c>
       <c r="B195" s="2">
-        <v>610010005597</v>
+        <v>610010005593</v>
       </c>
       <c r="C195" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D195">
         <v>5</v>
@@ -6171,10 +6171,10 @@
         <v>29</v>
       </c>
       <c r="B196" s="2">
-        <v>610010005594</v>
+        <v>610010005597</v>
       </c>
       <c r="C196" t="s">
-        <v>234</v>
+        <v>186</v>
       </c>
       <c r="D196">
         <v>5</v>
@@ -6194,10 +6194,10 @@
         <v>29</v>
       </c>
       <c r="B197" s="2">
-        <v>610010005596</v>
+        <v>610010005594</v>
       </c>
       <c r="C197" t="s">
-        <v>187</v>
+        <v>234</v>
       </c>
       <c r="D197">
         <v>5</v>
@@ -6217,10 +6217,10 @@
         <v>29</v>
       </c>
       <c r="B198" s="2">
-        <v>610010005595</v>
+        <v>610010005596</v>
       </c>
       <c r="C198" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D198">
         <v>5</v>
@@ -6240,10 +6240,10 @@
         <v>29</v>
       </c>
       <c r="B199" s="2">
-        <v>610010005649</v>
+        <v>610010005595</v>
       </c>
       <c r="C199" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D199">
         <v>5</v>
@@ -6263,10 +6263,10 @@
         <v>29</v>
       </c>
       <c r="B200" s="2">
-        <v>610010005648</v>
+        <v>610010005649</v>
       </c>
       <c r="C200" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D200">
         <v>5</v>
@@ -6286,10 +6286,10 @@
         <v>29</v>
       </c>
       <c r="B201" s="2">
-        <v>610010005647</v>
+        <v>610010005648</v>
       </c>
       <c r="C201" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D201">
         <v>5</v>
@@ -6309,19 +6309,19 @@
         <v>29</v>
       </c>
       <c r="B202" s="2">
-        <v>610010005584</v>
+        <v>610010005647</v>
       </c>
       <c r="C202" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D202">
         <v>5</v>
       </c>
       <c r="E202">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F202">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G202" t="s">
         <v>151</v>
@@ -6332,10 +6332,10 @@
         <v>29</v>
       </c>
       <c r="B203" s="2">
-        <v>610010005585</v>
+        <v>610010005584</v>
       </c>
       <c r="C203" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D203">
         <v>5</v>
@@ -6355,10 +6355,10 @@
         <v>29</v>
       </c>
       <c r="B204" s="2">
-        <v>610010005586</v>
+        <v>610010005585</v>
       </c>
       <c r="C204" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D204">
         <v>5</v>
@@ -6378,10 +6378,10 @@
         <v>29</v>
       </c>
       <c r="B205" s="2">
-        <v>610010005583</v>
+        <v>610010005586</v>
       </c>
       <c r="C205" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D205">
         <v>5</v>
@@ -6401,10 +6401,10 @@
         <v>29</v>
       </c>
       <c r="B206" s="2">
-        <v>610010005582</v>
+        <v>610010005583</v>
       </c>
       <c r="C206" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D206">
         <v>5</v>
@@ -6424,10 +6424,10 @@
         <v>29</v>
       </c>
       <c r="B207" s="2">
-        <v>610010005581</v>
+        <v>610010005582</v>
       </c>
       <c r="C207" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D207">
         <v>5</v>
@@ -6447,10 +6447,10 @@
         <v>29</v>
       </c>
       <c r="B208" s="2">
-        <v>610010005653</v>
+        <v>610010005581</v>
       </c>
       <c r="C208" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D208">
         <v>5</v>
@@ -6459,7 +6459,7 @@
         <v>6</v>
       </c>
       <c r="F208">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G208" t="s">
         <v>151</v>
@@ -6470,10 +6470,10 @@
         <v>29</v>
       </c>
       <c r="B209" s="2">
-        <v>610010005654</v>
+        <v>610010005653</v>
       </c>
       <c r="C209" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D209">
         <v>5</v>
@@ -6493,10 +6493,10 @@
         <v>29</v>
       </c>
       <c r="B210" s="2">
-        <v>610010005655</v>
+        <v>610010005654</v>
       </c>
       <c r="C210" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D210">
         <v>5</v>
@@ -6516,10 +6516,10 @@
         <v>29</v>
       </c>
       <c r="B211" s="2">
-        <v>610010005652</v>
+        <v>610010005655</v>
       </c>
       <c r="C211" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D211">
         <v>5</v>
@@ -6539,10 +6539,10 @@
         <v>29</v>
       </c>
       <c r="B212" s="2">
-        <v>610010005651</v>
+        <v>610010005652</v>
       </c>
       <c r="C212" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D212">
         <v>5</v>
@@ -6562,10 +6562,10 @@
         <v>29</v>
       </c>
       <c r="B213" s="2">
-        <v>610010005650</v>
+        <v>610010005651</v>
       </c>
       <c r="C213" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D213">
         <v>5</v>
@@ -6585,10 +6585,10 @@
         <v>29</v>
       </c>
       <c r="B214" s="2">
-        <v>610010005644</v>
+        <v>610010005650</v>
       </c>
       <c r="C214" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D214">
         <v>5</v>
@@ -6608,10 +6608,10 @@
         <v>29</v>
       </c>
       <c r="B215" s="2">
-        <v>610010005645</v>
+        <v>610010005644</v>
       </c>
       <c r="C215" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D215">
         <v>5</v>
@@ -6631,10 +6631,10 @@
         <v>29</v>
       </c>
       <c r="B216" s="2">
-        <v>610010005646</v>
+        <v>610010005645</v>
       </c>
       <c r="C216" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D216">
         <v>5</v>
@@ -6654,10 +6654,10 @@
         <v>29</v>
       </c>
       <c r="B217" s="2">
-        <v>610010005643</v>
+        <v>610010005646</v>
       </c>
       <c r="C217" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D217">
         <v>5</v>
@@ -6677,10 +6677,10 @@
         <v>29</v>
       </c>
       <c r="B218" s="2">
-        <v>610010005642</v>
+        <v>610010005643</v>
       </c>
       <c r="C218" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D218">
         <v>5</v>
@@ -6700,10 +6700,10 @@
         <v>29</v>
       </c>
       <c r="B219" s="2">
-        <v>610010005641</v>
+        <v>610010005642</v>
       </c>
       <c r="C219" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D219">
         <v>5</v>
@@ -6723,19 +6723,19 @@
         <v>29</v>
       </c>
       <c r="B220" s="2">
-        <v>600010000900</v>
+        <v>610010005641</v>
       </c>
       <c r="C220" t="s">
-        <v>235</v>
+        <v>197</v>
       </c>
       <c r="D220">
         <v>5</v>
       </c>
       <c r="E220">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F220">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G220" t="s">
         <v>151</v>
@@ -6746,19 +6746,19 @@
         <v>29</v>
       </c>
       <c r="B221" s="2">
-        <v>610010003037</v>
+        <v>600010000900</v>
       </c>
       <c r="C221" t="s">
-        <v>198</v>
+        <v>235</v>
       </c>
       <c r="D221">
         <v>5</v>
       </c>
       <c r="E221">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F221">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G221" t="s">
         <v>151</v>
@@ -6769,19 +6769,19 @@
         <v>29</v>
       </c>
       <c r="B222" s="2">
-        <v>610010003033</v>
+        <v>610010003037</v>
       </c>
       <c r="C222" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D222">
         <v>5</v>
       </c>
       <c r="E222">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F222">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G222" t="s">
         <v>151</v>
@@ -6792,19 +6792,19 @@
         <v>29</v>
       </c>
       <c r="B223" s="2">
-        <v>610010003036</v>
+        <v>610010003033</v>
       </c>
       <c r="C223" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D223">
         <v>5</v>
       </c>
       <c r="E223">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F223">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G223" t="s">
         <v>151</v>
@@ -6815,19 +6815,19 @@
         <v>29</v>
       </c>
       <c r="B224" s="2">
-        <v>600010000901</v>
+        <v>610010003036</v>
       </c>
       <c r="C224" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="D224">
         <v>5</v>
       </c>
       <c r="E224">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F224">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G224" t="s">
         <v>151</v>
@@ -6838,10 +6838,10 @@
         <v>29</v>
       </c>
       <c r="B225" s="2">
-        <v>610010004519</v>
+        <v>600010000901</v>
       </c>
       <c r="C225" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D225">
         <v>5</v>
@@ -6861,10 +6861,10 @@
         <v>29</v>
       </c>
       <c r="B226" s="2">
-        <v>610010004520</v>
+        <v>610010004519</v>
       </c>
       <c r="C226" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D226">
         <v>5</v>
@@ -6884,10 +6884,10 @@
         <v>29</v>
       </c>
       <c r="B227" s="2">
-        <v>610010004521</v>
+        <v>610010004520</v>
       </c>
       <c r="C227" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D227">
         <v>5</v>
@@ -6907,10 +6907,10 @@
         <v>29</v>
       </c>
       <c r="B228" s="2">
-        <v>610010004522</v>
+        <v>610010004521</v>
       </c>
       <c r="C228" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D228">
         <v>5</v>
@@ -6930,10 +6930,10 @@
         <v>29</v>
       </c>
       <c r="B229" s="2">
-        <v>610010004686</v>
+        <v>610010004522</v>
       </c>
       <c r="C229" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D229">
         <v>5</v>
@@ -6953,10 +6953,10 @@
         <v>29</v>
       </c>
       <c r="B230" s="2">
-        <v>610010004685</v>
+        <v>610010004686</v>
       </c>
       <c r="C230" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D230">
         <v>5</v>
@@ -6976,10 +6976,10 @@
         <v>29</v>
       </c>
       <c r="B231" s="2">
-        <v>610010004683</v>
+        <v>610010004685</v>
       </c>
       <c r="C231" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D231">
         <v>5</v>
@@ -6999,10 +6999,10 @@
         <v>29</v>
       </c>
       <c r="B232" s="2">
-        <v>610010004684</v>
+        <v>610010004683</v>
       </c>
       <c r="C232" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D232">
         <v>5</v>
@@ -7022,10 +7022,10 @@
         <v>29</v>
       </c>
       <c r="B233" s="2">
-        <v>610010004687</v>
+        <v>610010004684</v>
       </c>
       <c r="C233" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D233">
         <v>5</v>
@@ -7045,19 +7045,19 @@
         <v>29</v>
       </c>
       <c r="B234" s="2">
-        <v>610010005859</v>
+        <v>610010004687</v>
       </c>
       <c r="C234" t="s">
-        <v>201</v>
+        <v>245</v>
       </c>
       <c r="D234">
         <v>5</v>
       </c>
       <c r="E234">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F234">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G234" t="s">
         <v>151</v>
@@ -7068,19 +7068,19 @@
         <v>29</v>
       </c>
       <c r="B235" s="2">
-        <v>610010005782</v>
+        <v>610010005859</v>
       </c>
       <c r="C235" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D235">
         <v>5</v>
       </c>
       <c r="E235">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F235">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G235" t="s">
         <v>151</v>
@@ -7091,19 +7091,19 @@
         <v>29</v>
       </c>
       <c r="B236" s="2">
-        <v>610010005862</v>
+        <v>610010005782</v>
       </c>
       <c r="C236" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D236">
         <v>5</v>
       </c>
       <c r="E236">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F236">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G236" t="s">
         <v>151</v>
@@ -7114,19 +7114,19 @@
         <v>29</v>
       </c>
       <c r="B237" s="2">
-        <v>610010005780</v>
+        <v>610010005862</v>
       </c>
       <c r="C237" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D237">
         <v>5</v>
       </c>
       <c r="E237">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F237">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G237" t="s">
         <v>151</v>
@@ -7137,19 +7137,19 @@
         <v>29</v>
       </c>
       <c r="B238" s="2">
-        <v>610010005860</v>
+        <v>610010005780</v>
       </c>
       <c r="C238" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D238">
         <v>5</v>
       </c>
       <c r="E238">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F238">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G238" t="s">
         <v>151</v>
@@ -7160,19 +7160,19 @@
         <v>29</v>
       </c>
       <c r="B239" s="2">
-        <v>610010005778</v>
+        <v>610010005860</v>
       </c>
       <c r="C239" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D239">
         <v>5</v>
       </c>
       <c r="E239">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F239">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G239" t="s">
         <v>151</v>
@@ -7183,19 +7183,19 @@
         <v>29</v>
       </c>
       <c r="B240" s="2">
-        <v>610010005858</v>
+        <v>610010005778</v>
       </c>
       <c r="C240" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D240">
         <v>5</v>
       </c>
       <c r="E240">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F240">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G240" t="s">
         <v>151</v>
@@ -7206,16 +7206,16 @@
         <v>29</v>
       </c>
       <c r="B241" s="2">
-        <v>610010005871</v>
+        <v>610010005858</v>
       </c>
       <c r="C241" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="D241">
         <v>5</v>
       </c>
       <c r="E241">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F241">
         <v>35</v>
@@ -7229,10 +7229,10 @@
         <v>29</v>
       </c>
       <c r="B242" s="2">
-        <v>610010005869</v>
+        <v>610010005871</v>
       </c>
       <c r="C242" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D242">
         <v>5</v>
@@ -7241,7 +7241,7 @@
         <v>7</v>
       </c>
       <c r="F242">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G242" t="s">
         <v>151</v>
@@ -7252,10 +7252,10 @@
         <v>29</v>
       </c>
       <c r="B243" s="2">
-        <v>610010005872</v>
+        <v>610010005869</v>
       </c>
       <c r="C243" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D243">
         <v>5</v>
@@ -7275,10 +7275,10 @@
         <v>29</v>
       </c>
       <c r="B244" s="2">
-        <v>610010005870</v>
+        <v>610010005872</v>
       </c>
       <c r="C244" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D244">
         <v>5</v>
@@ -7298,10 +7298,10 @@
         <v>29</v>
       </c>
       <c r="B245" s="2">
-        <v>610010005868</v>
+        <v>610010005870</v>
       </c>
       <c r="C245" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D245">
         <v>5</v>
@@ -7321,16 +7321,16 @@
         <v>29</v>
       </c>
       <c r="B246" s="2">
-        <v>610010005861</v>
+        <v>610010005868</v>
       </c>
       <c r="C246" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="D246">
         <v>5</v>
       </c>
       <c r="E246">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F246">
         <v>40</v>
@@ -7344,16 +7344,16 @@
         <v>29</v>
       </c>
       <c r="B247" s="2">
-        <v>610010005857</v>
+        <v>610010005861</v>
       </c>
       <c r="C247" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D247">
         <v>5</v>
       </c>
       <c r="E247">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F247">
         <v>40</v>
@@ -7367,10 +7367,10 @@
         <v>29</v>
       </c>
       <c r="B248" s="2">
-        <v>600010002006</v>
+        <v>610010005857</v>
       </c>
       <c r="C248" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="D248">
         <v>5</v>
@@ -7390,10 +7390,10 @@
         <v>29</v>
       </c>
       <c r="B249" s="2">
-        <v>610010006099</v>
+        <v>600010002006</v>
       </c>
       <c r="C249" t="s">
-        <v>210</v>
+        <v>246</v>
       </c>
       <c r="D249">
         <v>5</v>
@@ -7413,19 +7413,19 @@
         <v>29</v>
       </c>
       <c r="B250" s="2">
-        <v>610010006051</v>
+        <v>610010006099</v>
       </c>
       <c r="C250" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D250">
         <v>5</v>
       </c>
       <c r="E250">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F250">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G250" t="s">
         <v>151</v>
@@ -7436,10 +7436,10 @@
         <v>29</v>
       </c>
       <c r="B251" s="2">
-        <v>610010006052</v>
+        <v>610010006051</v>
       </c>
       <c r="C251" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D251">
         <v>5</v>
@@ -7459,19 +7459,19 @@
         <v>29</v>
       </c>
       <c r="B252" s="2">
-        <v>610010006095</v>
+        <v>610010006052</v>
       </c>
       <c r="C252" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D252">
         <v>5</v>
       </c>
       <c r="E252">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F252">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G252" t="s">
         <v>151</v>
@@ -7482,7 +7482,7 @@
         <v>29</v>
       </c>
       <c r="B253" s="2">
-        <v>610010006037</v>
+        <v>610010006095</v>
       </c>
       <c r="C253" t="s">
         <v>213</v>
@@ -7491,10 +7491,10 @@
         <v>5</v>
       </c>
       <c r="E253">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F253">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G253" t="s">
         <v>151</v>
@@ -7505,19 +7505,19 @@
         <v>29</v>
       </c>
       <c r="B254" s="2">
-        <v>610010005783</v>
+        <v>610010006037</v>
       </c>
       <c r="C254" t="s">
-        <v>247</v>
+        <v>213</v>
       </c>
       <c r="D254">
         <v>5</v>
       </c>
       <c r="E254">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F254">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G254" t="s">
         <v>151</v>
@@ -7528,10 +7528,10 @@
         <v>29</v>
       </c>
       <c r="B255" s="2">
-        <v>610010005785</v>
+        <v>610010005783</v>
       </c>
       <c r="C255" t="s">
-        <v>276</v>
+        <v>247</v>
       </c>
       <c r="D255">
         <v>5</v>
@@ -7551,19 +7551,19 @@
         <v>29</v>
       </c>
       <c r="B256" s="2">
-        <v>610010005784</v>
+        <v>610010005785</v>
       </c>
       <c r="C256" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="D256">
         <v>5</v>
       </c>
       <c r="E256">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F256">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G256" t="s">
         <v>151</v>
@@ -7574,19 +7574,19 @@
         <v>29</v>
       </c>
       <c r="B257" s="2">
-        <v>610010005272</v>
+        <v>610010005784</v>
       </c>
       <c r="C257" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D257">
         <v>5</v>
       </c>
       <c r="E257">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F257">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G257" t="s">
         <v>151</v>
@@ -7597,19 +7597,19 @@
         <v>29</v>
       </c>
       <c r="B258" s="2">
-        <v>600010000952</v>
+        <v>610010005272</v>
       </c>
       <c r="C258" t="s">
-        <v>214</v>
+        <v>251</v>
       </c>
       <c r="D258">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E258">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F258">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="G258" t="s">
         <v>151</v>
@@ -7620,19 +7620,19 @@
         <v>29</v>
       </c>
       <c r="B259" s="2">
-        <v>600010010197</v>
+        <v>600010000952</v>
       </c>
       <c r="C259" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D259">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E259">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F259">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="G259" t="s">
         <v>151</v>
@@ -7643,19 +7643,19 @@
         <v>29</v>
       </c>
       <c r="B260" s="2">
-        <v>610010001901</v>
+        <v>600010010197</v>
       </c>
       <c r="C260" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D260">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E260">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F260">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="G260" t="s">
         <v>151</v>
@@ -7666,19 +7666,19 @@
         <v>29</v>
       </c>
       <c r="B261" s="2">
-        <v>610010001900</v>
+        <v>610010001901</v>
       </c>
       <c r="C261" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D261">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E261">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F261">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="G261" t="s">
         <v>151</v>
@@ -7689,19 +7689,19 @@
         <v>29</v>
       </c>
       <c r="B262" s="2">
-        <v>600110000239</v>
+        <v>610010001900</v>
       </c>
       <c r="C262" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="D262">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E262">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F262">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G262" t="s">
         <v>151</v>
@@ -7712,19 +7712,19 @@
         <v>29</v>
       </c>
       <c r="B263" s="2">
-        <v>610110000595</v>
+        <v>600110000239</v>
       </c>
       <c r="C263" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D263">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E263">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F263">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G263" t="s">
         <v>151</v>
@@ -7735,19 +7735,19 @@
         <v>29</v>
       </c>
       <c r="B264" s="2">
-        <v>610110000591</v>
+        <v>610110000595</v>
       </c>
       <c r="C264" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D264">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E264">
         <v>5</v>
       </c>
       <c r="F264">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G264" t="s">
         <v>151</v>
@@ -7758,19 +7758,19 @@
         <v>29</v>
       </c>
       <c r="B265" s="2">
-        <v>610110000340</v>
+        <v>610110000591</v>
       </c>
       <c r="C265" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D265">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E265">
         <v>5</v>
       </c>
       <c r="F265">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="G265" t="s">
         <v>151</v>
@@ -7781,19 +7781,19 @@
         <v>29</v>
       </c>
       <c r="B266" s="2">
-        <v>610110000594</v>
+        <v>610110000340</v>
       </c>
       <c r="C266" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="D266">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E266">
         <v>5</v>
       </c>
       <c r="F266">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G266" t="s">
         <v>151</v>
@@ -7804,19 +7804,19 @@
         <v>29</v>
       </c>
       <c r="B267" s="2">
-        <v>610110000590</v>
+        <v>610110000594</v>
       </c>
       <c r="C267" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D267">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E267">
         <v>5</v>
       </c>
       <c r="F267">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G267" t="s">
         <v>151</v>
@@ -7827,19 +7827,19 @@
         <v>29</v>
       </c>
       <c r="B268" s="2">
-        <v>600110000240</v>
+        <v>610110000590</v>
       </c>
       <c r="C268" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D268">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E268">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F268">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="G268" t="s">
         <v>151</v>
@@ -7850,16 +7850,16 @@
         <v>29</v>
       </c>
       <c r="B269" s="2">
-        <v>610110000336</v>
+        <v>600110000240</v>
       </c>
       <c r="C269" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D269">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E269">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F269">
         <v>36</v>
@@ -7873,10 +7873,10 @@
         <v>29</v>
       </c>
       <c r="B270" s="2">
-        <v>610110000335</v>
+        <v>610110000336</v>
       </c>
       <c r="C270" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D270">
         <v>8</v>
@@ -7896,19 +7896,19 @@
         <v>29</v>
       </c>
       <c r="B271" s="2">
-        <v>610110000593</v>
+        <v>610110000335</v>
       </c>
       <c r="C271" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D271">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E271">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F271">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G271" t="s">
         <v>151</v>
@@ -7919,16 +7919,16 @@
         <v>29</v>
       </c>
       <c r="B272" s="2">
-        <v>600110000824</v>
+        <v>610110000593</v>
       </c>
       <c r="C272" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D272">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E272">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F272">
         <v>40</v>
@@ -7942,19 +7942,19 @@
         <v>29</v>
       </c>
       <c r="B273" s="2">
-        <v>600110000798</v>
+        <v>600110000824</v>
       </c>
       <c r="C273" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="D273">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E273">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F273">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G273" t="s">
         <v>151</v>
@@ -7965,19 +7965,19 @@
         <v>29</v>
       </c>
       <c r="B274" s="2">
-        <v>600110000823</v>
+        <v>600110000798</v>
       </c>
       <c r="C274" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D274">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E274">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F274">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G274" t="s">
         <v>151</v>
@@ -7988,19 +7988,19 @@
         <v>29</v>
       </c>
       <c r="B275" s="2">
-        <v>610110001004</v>
+        <v>600110000823</v>
       </c>
       <c r="C275" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D275">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E275">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F275">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G275" t="s">
         <v>151</v>
@@ -8011,10 +8011,10 @@
         <v>29</v>
       </c>
       <c r="B276" s="2">
-        <v>610110001006</v>
+        <v>610110001004</v>
       </c>
       <c r="C276" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D276">
         <v>14</v>
@@ -8034,10 +8034,10 @@
         <v>29</v>
       </c>
       <c r="B277" s="2">
-        <v>610110001003</v>
+        <v>610110001006</v>
       </c>
       <c r="C277" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="D277">
         <v>14</v>
@@ -8057,10 +8057,10 @@
         <v>29</v>
       </c>
       <c r="B278" s="2">
-        <v>610110001005</v>
+        <v>610110001003</v>
       </c>
       <c r="C278" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="D278">
         <v>14</v>
@@ -8080,19 +8080,19 @@
         <v>29</v>
       </c>
       <c r="B279" s="2">
-        <v>610110000990</v>
+        <v>610110001005</v>
       </c>
       <c r="C279" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D279">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E279">
         <v>5</v>
       </c>
       <c r="F279">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G279" t="s">
         <v>151</v>
@@ -8103,10 +8103,10 @@
         <v>29</v>
       </c>
       <c r="B280" s="2">
-        <v>610110000996</v>
+        <v>610110000990</v>
       </c>
       <c r="C280" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D280">
         <v>15</v>
@@ -8126,19 +8126,19 @@
         <v>29</v>
       </c>
       <c r="B281" s="2">
-        <v>610110001508</v>
+        <v>610110000996</v>
       </c>
       <c r="C281" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D281">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E281">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F281">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="G281" t="s">
         <v>151</v>
@@ -8149,19 +8149,19 @@
         <v>29</v>
       </c>
       <c r="B282" s="2">
-        <v>610110000994</v>
+        <v>610110001508</v>
       </c>
       <c r="C282" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D282">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E282">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F282">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="G282" t="s">
         <v>151</v>
@@ -8172,10 +8172,10 @@
         <v>29</v>
       </c>
       <c r="B283" s="2">
-        <v>610110000992</v>
+        <v>610110000994</v>
       </c>
       <c r="C283" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D283">
         <v>15</v>
@@ -8195,10 +8195,10 @@
         <v>29</v>
       </c>
       <c r="B284" s="2">
-        <v>610110000991</v>
+        <v>610110000992</v>
       </c>
       <c r="C284" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D284">
         <v>15</v>
@@ -8218,10 +8218,10 @@
         <v>29</v>
       </c>
       <c r="B285" s="2">
-        <v>610110000989</v>
+        <v>610110000991</v>
       </c>
       <c r="C285" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D285">
         <v>15</v>
@@ -8241,10 +8241,10 @@
         <v>29</v>
       </c>
       <c r="B286" s="2">
-        <v>610110000993</v>
+        <v>610110000989</v>
       </c>
       <c r="C286" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D286">
         <v>15</v>
@@ -8264,10 +8264,10 @@
         <v>29</v>
       </c>
       <c r="B287" s="2">
-        <v>610110000988</v>
+        <v>610110000993</v>
       </c>
       <c r="C287" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D287">
         <v>15</v>
@@ -8282,27 +8282,50 @@
         <v>151</v>
       </c>
     </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A288" t="s">
+        <v>29</v>
+      </c>
+      <c r="B288" s="2">
+        <v>610110000988</v>
+      </c>
+      <c r="C288" t="s">
+        <v>274</v>
+      </c>
+      <c r="D288">
+        <v>15</v>
+      </c>
+      <c r="E288">
+        <v>5</v>
+      </c>
+      <c r="F288">
+        <v>60</v>
+      </c>
+      <c r="G288" t="s">
+        <v>151</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F163" xr:uid="{F30446A3-A986-4686-A765-4C12AB9F4FB1}"/>
-  <conditionalFormatting sqref="B2:B144">
+  <autoFilter ref="A1:F164" xr:uid="{F30446A3-A986-4686-A765-4C12AB9F4FB1}"/>
+  <conditionalFormatting sqref="B2:B145">
     <cfRule type="duplicateValues" dxfId="1" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B148:B149 B153:B154 B158:B159 B163">
+  <conditionalFormatting sqref="B149:B150 B154:B155 B159:B160 B164">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="C10" r:id="rId1" xr:uid="{89506ED6-C4FD-47B8-9FD6-878DCA92E9AA}"/>
     <hyperlink ref="C21" r:id="rId2" xr:uid="{7B1ECE4D-B039-4F94-838C-A478D53267E0}"/>
-    <hyperlink ref="C90" r:id="rId3" xr:uid="{DBB2C1A8-C8F2-410F-A78B-A3CD9BB920C8}"/>
-    <hyperlink ref="C102" r:id="rId4" xr:uid="{DD3336F3-63B5-4EA8-91C3-0AEEB13315C2}"/>
-    <hyperlink ref="C110" r:id="rId5" xr:uid="{8BD8BB4A-70AA-4FA9-9A46-A3355CDFBD57}"/>
-    <hyperlink ref="C103" r:id="rId6" xr:uid="{4FEA0A94-1AD0-4B82-ABB9-6EDBB77929EF}"/>
-    <hyperlink ref="C111:C113" r:id="rId7" display="Bluestone Natural Cleft 24x24" xr:uid="{9D1D11EE-261B-43AD-B4EF-C3FA544A4E70}"/>
-    <hyperlink ref="C120" r:id="rId8" xr:uid="{D42B3E22-C339-41A5-BEA6-DF49B989F449}"/>
-    <hyperlink ref="C122" r:id="rId9" xr:uid="{2B8374D8-0246-4EE4-B96B-FFB02E40BDD1}"/>
-    <hyperlink ref="C111" r:id="rId10" xr:uid="{14C18384-D389-4B97-8461-5247EE585E74}"/>
-    <hyperlink ref="C112" r:id="rId11" xr:uid="{9272B80D-012D-439F-9BD1-11D9279BF6BE}"/>
-    <hyperlink ref="C113" r:id="rId12" xr:uid="{382FF713-4781-44B6-B266-152BC4F3E727}"/>
+    <hyperlink ref="C91" r:id="rId3" xr:uid="{DBB2C1A8-C8F2-410F-A78B-A3CD9BB920C8}"/>
+    <hyperlink ref="C103" r:id="rId4" xr:uid="{DD3336F3-63B5-4EA8-91C3-0AEEB13315C2}"/>
+    <hyperlink ref="C111" r:id="rId5" xr:uid="{8BD8BB4A-70AA-4FA9-9A46-A3355CDFBD57}"/>
+    <hyperlink ref="C104" r:id="rId6" xr:uid="{4FEA0A94-1AD0-4B82-ABB9-6EDBB77929EF}"/>
+    <hyperlink ref="C112:C114" r:id="rId7" display="Bluestone Natural Cleft 24x24" xr:uid="{9D1D11EE-261B-43AD-B4EF-C3FA544A4E70}"/>
+    <hyperlink ref="C121" r:id="rId8" xr:uid="{D42B3E22-C339-41A5-BEA6-DF49B989F449}"/>
+    <hyperlink ref="C123" r:id="rId9" xr:uid="{2B8374D8-0246-4EE4-B96B-FFB02E40BDD1}"/>
+    <hyperlink ref="C112" r:id="rId10" xr:uid="{14C18384-D389-4B97-8461-5247EE585E74}"/>
+    <hyperlink ref="C113" r:id="rId11" xr:uid="{9272B80D-012D-439F-9BD1-11D9279BF6BE}"/>
+    <hyperlink ref="C114" r:id="rId12" xr:uid="{382FF713-4781-44B6-B266-152BC4F3E727}"/>
     <hyperlink ref="C11" r:id="rId13" xr:uid="{3F2A552B-E241-4F03-BD67-4202AAA8FE8E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/LTL_qty_updated_7.28.26.xlsx
+++ b/LTL_qty_updated_7.28.26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acusa-my.sharepoint.com/personal/g_ghedini_atlasconcordeusa_com/Documents/Desktop/AI - Automations/BOL creation/SAP_cleaning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{6160EAF0-1319-425F-818F-4192C3B46458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A679F11A-D80B-4578-8C3B-069CD43A4790}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{6160EAF0-1319-425F-818F-4192C3B46458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9734E999-E00E-4F53-93BA-320FA25B009A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B388D9E8-F042-4987-BDB7-8E3EC1CFA04A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$165</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="277">
   <si>
     <t>D23_Floor and Wall Tiles</t>
   </si>
@@ -1756,7 +1756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F30446A3-A986-4686-A765-4C12AB9F4FB1}">
-  <dimension ref="A1:G288"/>
+  <dimension ref="A1:G289"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
@@ -2953,16 +2953,19 @@
         <v>29</v>
       </c>
       <c r="B54" s="8">
-        <v>610010004572</v>
+        <v>600010000910</v>
       </c>
       <c r="C54" t="s">
-        <v>123</v>
+        <v>65</v>
+      </c>
+      <c r="D54">
+        <v>5</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F54">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G54" t="s">
         <v>151</v>
@@ -2973,19 +2976,16 @@
         <v>29</v>
       </c>
       <c r="B55" s="8">
-        <v>610010001043</v>
+        <v>610010004572</v>
       </c>
       <c r="C55" t="s">
-        <v>66</v>
-      </c>
-      <c r="D55">
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="E55">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F55">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G55" t="s">
         <v>151</v>
@@ -2996,16 +2996,19 @@
         <v>29</v>
       </c>
       <c r="B56" s="8">
-        <v>610010004575</v>
+        <v>610010001043</v>
       </c>
       <c r="C56" t="s">
-        <v>124</v>
+        <v>66</v>
+      </c>
+      <c r="D56">
+        <v>5</v>
       </c>
       <c r="E56">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F56">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G56" t="s">
         <v>151</v>
@@ -3016,19 +3019,16 @@
         <v>29</v>
       </c>
       <c r="B57" s="8">
-        <v>610010001039</v>
+        <v>610010004575</v>
       </c>
       <c r="C57" t="s">
-        <v>67</v>
-      </c>
-      <c r="D57">
-        <v>5</v>
+        <v>124</v>
       </c>
       <c r="E57">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F57">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G57" t="s">
         <v>151</v>
@@ -3039,16 +3039,19 @@
         <v>29</v>
       </c>
       <c r="B58" s="8">
-        <v>610010004571</v>
-      </c>
-      <c r="C58" s="12" t="s">
-        <v>125</v>
+        <v>610010001039</v>
+      </c>
+      <c r="C58" t="s">
+        <v>67</v>
+      </c>
+      <c r="D58">
+        <v>5</v>
       </c>
       <c r="E58">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F58">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G58" t="s">
         <v>151</v>
@@ -3059,19 +3062,16 @@
         <v>29</v>
       </c>
       <c r="B59" s="8">
-        <v>610010005313</v>
-      </c>
-      <c r="C59" t="s">
-        <v>68</v>
-      </c>
-      <c r="D59">
-        <v>19</v>
+        <v>610010004571</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>125</v>
       </c>
       <c r="E59">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F59">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="G59" t="s">
         <v>151</v>
@@ -3082,19 +3082,19 @@
         <v>29</v>
       </c>
       <c r="B60" s="8">
-        <v>610010005274</v>
+        <v>610010005313</v>
       </c>
       <c r="C60" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D60">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E60">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F60">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="G60" t="s">
         <v>151</v>
@@ -3105,16 +3105,19 @@
         <v>29</v>
       </c>
       <c r="B61" s="8">
-        <v>610010005283</v>
+        <v>610010005274</v>
       </c>
       <c r="C61" t="s">
-        <v>126</v>
+        <v>69</v>
+      </c>
+      <c r="D61">
+        <v>5</v>
       </c>
       <c r="E61">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F61">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G61" t="s">
         <v>151</v>
@@ -3125,19 +3128,16 @@
         <v>29</v>
       </c>
       <c r="B62" s="8">
-        <v>610010005319</v>
+        <v>610010005283</v>
       </c>
       <c r="C62" t="s">
-        <v>70</v>
-      </c>
-      <c r="D62">
-        <v>19</v>
+        <v>126</v>
       </c>
       <c r="E62">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F62">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="G62" t="s">
         <v>151</v>
@@ -3148,19 +3148,19 @@
         <v>29</v>
       </c>
       <c r="B63" s="8">
-        <v>610010005280</v>
+        <v>610010005319</v>
       </c>
       <c r="C63" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D63">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E63">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F63">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="G63" t="s">
         <v>151</v>
@@ -3171,16 +3171,19 @@
         <v>29</v>
       </c>
       <c r="B64" s="8">
-        <v>610010005289</v>
+        <v>610010005280</v>
       </c>
       <c r="C64" t="s">
-        <v>127</v>
+        <v>71</v>
+      </c>
+      <c r="D64">
+        <v>5</v>
       </c>
       <c r="E64">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F64">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G64" t="s">
         <v>151</v>
@@ -3191,19 +3194,16 @@
         <v>29</v>
       </c>
       <c r="B65" s="8">
-        <v>610010005317</v>
+        <v>610010005289</v>
       </c>
       <c r="C65" t="s">
-        <v>72</v>
-      </c>
-      <c r="D65">
-        <v>19</v>
+        <v>127</v>
       </c>
       <c r="E65">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F65">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="G65" t="s">
         <v>151</v>
@@ -3214,19 +3214,19 @@
         <v>29</v>
       </c>
       <c r="B66" s="8">
-        <v>610010005278</v>
+        <v>610010005317</v>
       </c>
       <c r="C66" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D66">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E66">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F66">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="G66" t="s">
         <v>151</v>
@@ -3237,16 +3237,19 @@
         <v>29</v>
       </c>
       <c r="B67" s="8">
-        <v>610010005287</v>
+        <v>610010005278</v>
       </c>
       <c r="C67" t="s">
-        <v>128</v>
+        <v>73</v>
+      </c>
+      <c r="D67">
+        <v>5</v>
       </c>
       <c r="E67">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F67">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G67" t="s">
         <v>151</v>
@@ -3257,19 +3260,16 @@
         <v>29</v>
       </c>
       <c r="B68" s="8">
-        <v>610010005318</v>
+        <v>610010005287</v>
       </c>
       <c r="C68" t="s">
-        <v>74</v>
-      </c>
-      <c r="D68">
-        <v>19</v>
+        <v>128</v>
       </c>
       <c r="E68">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F68">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="G68" t="s">
         <v>151</v>
@@ -3280,19 +3280,19 @@
         <v>29</v>
       </c>
       <c r="B69" s="8">
-        <v>610010005279</v>
+        <v>610010005318</v>
       </c>
       <c r="C69" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D69">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E69">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F69">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="G69" t="s">
         <v>151</v>
@@ -3303,16 +3303,19 @@
         <v>29</v>
       </c>
       <c r="B70" s="8">
-        <v>610010005288</v>
+        <v>610010005279</v>
       </c>
       <c r="C70" t="s">
-        <v>129</v>
+        <v>75</v>
+      </c>
+      <c r="D70">
+        <v>5</v>
       </c>
       <c r="E70">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F70">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G70" t="s">
         <v>151</v>
@@ -3323,19 +3326,16 @@
         <v>29</v>
       </c>
       <c r="B71" s="8">
-        <v>610010005314</v>
+        <v>610010005288</v>
       </c>
       <c r="C71" t="s">
-        <v>76</v>
-      </c>
-      <c r="D71">
-        <v>19</v>
+        <v>129</v>
       </c>
       <c r="E71">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F71">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="G71" t="s">
         <v>151</v>
@@ -3346,19 +3346,19 @@
         <v>29</v>
       </c>
       <c r="B72" s="8">
-        <v>610010005275</v>
+        <v>610010005314</v>
       </c>
       <c r="C72" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D72">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E72">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F72">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="G72" t="s">
         <v>151</v>
@@ -3369,16 +3369,19 @@
         <v>29</v>
       </c>
       <c r="B73" s="8">
-        <v>610010005284</v>
+        <v>610010005275</v>
       </c>
       <c r="C73" t="s">
-        <v>130</v>
+        <v>77</v>
+      </c>
+      <c r="D73">
+        <v>5</v>
       </c>
       <c r="E73">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F73">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G73" t="s">
         <v>151</v>
@@ -3388,20 +3391,17 @@
       <c r="A74" t="s">
         <v>29</v>
       </c>
-      <c r="B74" s="2">
-        <v>610130007000</v>
-      </c>
-      <c r="C74" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D74">
-        <v>15</v>
+      <c r="B74" s="8">
+        <v>610010005284</v>
+      </c>
+      <c r="C74" t="s">
+        <v>130</v>
       </c>
       <c r="E74">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F74">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G74" t="s">
         <v>151</v>
@@ -3412,10 +3412,10 @@
         <v>29</v>
       </c>
       <c r="B75" s="2">
-        <v>610130000920</v>
+        <v>610130007000</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D75">
         <v>15</v>
@@ -3435,10 +3435,10 @@
         <v>29</v>
       </c>
       <c r="B76" s="2">
-        <v>610130007215</v>
+        <v>610130000920</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D76">
         <v>15</v>
@@ -3458,10 +3458,10 @@
         <v>29</v>
       </c>
       <c r="B77" s="2">
-        <v>610130007001</v>
+        <v>610130007215</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D77">
         <v>15</v>
@@ -3481,10 +3481,10 @@
         <v>29</v>
       </c>
       <c r="B78" s="2">
-        <v>610130000919</v>
+        <v>610130007001</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D78">
         <v>15</v>
@@ -3504,19 +3504,19 @@
         <v>29</v>
       </c>
       <c r="B79" s="2">
-        <v>610010002391</v>
-      </c>
-      <c r="C79" t="s">
-        <v>78</v>
+        <v>610130000919</v>
+      </c>
+      <c r="C79" s="14" t="s">
+        <v>26</v>
       </c>
       <c r="D79">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E79">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F79">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="G79" t="s">
         <v>151</v>
@@ -3527,10 +3527,10 @@
         <v>29</v>
       </c>
       <c r="B80" s="2">
-        <v>610010002393</v>
+        <v>610010002391</v>
       </c>
       <c r="C80" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D80">
         <v>6</v>
@@ -3550,10 +3550,10 @@
         <v>29</v>
       </c>
       <c r="B81" s="2">
-        <v>610010002392</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>80</v>
+        <v>610010002393</v>
+      </c>
+      <c r="C81" t="s">
+        <v>79</v>
       </c>
       <c r="D81">
         <v>6</v>
@@ -3573,19 +3573,19 @@
         <v>29</v>
       </c>
       <c r="B82" s="2">
-        <v>610010004527</v>
-      </c>
-      <c r="C82" t="s">
-        <v>81</v>
+        <v>610010002392</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="D82">
         <v>6</v>
       </c>
       <c r="E82">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F82">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="G82" t="s">
         <v>151</v>
@@ -3596,10 +3596,10 @@
         <v>29</v>
       </c>
       <c r="B83" s="2">
-        <v>610010004530</v>
+        <v>610010004527</v>
       </c>
       <c r="C83" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D83">
         <v>6</v>
@@ -3619,10 +3619,10 @@
         <v>29</v>
       </c>
       <c r="B84" s="2">
-        <v>610010004905</v>
+        <v>610010004530</v>
       </c>
       <c r="C84" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D84">
         <v>6</v>
@@ -3642,10 +3642,10 @@
         <v>29</v>
       </c>
       <c r="B85" s="2">
-        <v>610010002361</v>
+        <v>610010004905</v>
       </c>
       <c r="C85" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D85">
         <v>6</v>
@@ -3665,10 +3665,10 @@
         <v>29</v>
       </c>
       <c r="B86" s="2">
-        <v>610010004901</v>
+        <v>610010002361</v>
       </c>
       <c r="C86" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D86">
         <v>6</v>
@@ -3688,10 +3688,10 @@
         <v>29</v>
       </c>
       <c r="B87" s="2">
-        <v>610010004900</v>
+        <v>610010004901</v>
       </c>
       <c r="C87" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D87">
         <v>6</v>
@@ -3711,10 +3711,10 @@
         <v>29</v>
       </c>
       <c r="B88" s="2">
-        <v>610010004902</v>
-      </c>
-      <c r="C88" s="14" t="s">
-        <v>87</v>
+        <v>610010004900</v>
+      </c>
+      <c r="C88" t="s">
+        <v>86</v>
       </c>
       <c r="D88">
         <v>6</v>
@@ -3734,10 +3734,10 @@
         <v>29</v>
       </c>
       <c r="B89" s="2">
-        <v>610010004906</v>
+        <v>610010004902</v>
       </c>
       <c r="C89" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D89">
         <v>6</v>
@@ -3757,10 +3757,10 @@
         <v>29</v>
       </c>
       <c r="B90" s="2">
-        <v>610010002360</v>
+        <v>610010004906</v>
       </c>
       <c r="C90" s="14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D90">
         <v>6</v>
@@ -3779,11 +3779,11 @@
       <c r="A91" t="s">
         <v>29</v>
       </c>
-      <c r="B91" s="5">
-        <v>610010002851</v>
+      <c r="B91" s="2">
+        <v>610010002360</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="D91">
         <v>6</v>
@@ -3792,21 +3792,21 @@
         <v>29</v>
       </c>
       <c r="F91">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G91" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>29</v>
       </c>
-      <c r="B92" s="2">
-        <v>610010004582</v>
+      <c r="B92" s="5">
+        <v>610010002851</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="D92">
         <v>6</v>
@@ -3815,10 +3815,10 @@
         <v>29</v>
       </c>
       <c r="F92">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G92" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
@@ -3826,10 +3826,10 @@
         <v>29</v>
       </c>
       <c r="B93" s="2">
-        <v>610010004581</v>
-      </c>
-      <c r="C93" t="s">
-        <v>91</v>
+        <v>610010004582</v>
+      </c>
+      <c r="C93" s="14" t="s">
+        <v>90</v>
       </c>
       <c r="D93">
         <v>6</v>
@@ -3849,10 +3849,10 @@
         <v>29</v>
       </c>
       <c r="B94" s="2">
-        <v>610010004580</v>
+        <v>610010004581</v>
       </c>
       <c r="C94" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D94">
         <v>6</v>
@@ -3872,10 +3872,10 @@
         <v>29</v>
       </c>
       <c r="B95" s="2">
-        <v>610010004532</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>93</v>
+        <v>610010004580</v>
+      </c>
+      <c r="C95" t="s">
+        <v>92</v>
       </c>
       <c r="D95">
         <v>6</v>
@@ -3895,10 +3895,10 @@
         <v>29</v>
       </c>
       <c r="B96" s="2">
-        <v>610010002362</v>
-      </c>
-      <c r="C96" t="s">
-        <v>94</v>
+        <v>610010004532</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="D96">
         <v>6</v>
@@ -3918,10 +3918,10 @@
         <v>29</v>
       </c>
       <c r="B97" s="2">
-        <v>610010004903</v>
+        <v>610010002362</v>
       </c>
       <c r="C97" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D97">
         <v>6</v>
@@ -3941,10 +3941,10 @@
         <v>29</v>
       </c>
       <c r="B98" s="2">
-        <v>610010002814</v>
+        <v>610010004903</v>
       </c>
       <c r="C98" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D98">
         <v>6</v>
@@ -3964,10 +3964,10 @@
         <v>29</v>
       </c>
       <c r="B99" s="2">
-        <v>610010002816</v>
-      </c>
-      <c r="C99" s="14" t="s">
-        <v>97</v>
+        <v>610010002814</v>
+      </c>
+      <c r="C99" t="s">
+        <v>96</v>
       </c>
       <c r="D99">
         <v>6</v>
@@ -3987,10 +3987,10 @@
         <v>29</v>
       </c>
       <c r="B100" s="2">
-        <v>610010002815</v>
+        <v>610010002816</v>
       </c>
       <c r="C100" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D100">
         <v>6</v>
@@ -4010,10 +4010,10 @@
         <v>29</v>
       </c>
       <c r="B101" s="2">
-        <v>610010002817</v>
+        <v>610010002815</v>
       </c>
       <c r="C101" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D101">
         <v>6</v>
@@ -4033,16 +4033,16 @@
         <v>29</v>
       </c>
       <c r="B102" s="2">
-        <v>610110001402</v>
+        <v>610010002817</v>
       </c>
       <c r="C102" s="14" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="D102">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E102">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F102">
         <v>36</v>
@@ -4053,22 +4053,22 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B103" s="2">
-        <v>600010000961</v>
+        <v>610110001402</v>
       </c>
       <c r="C103" s="14" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D103">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F103">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="G103" t="s">
         <v>151</v>
@@ -4079,19 +4079,19 @@
         <v>30</v>
       </c>
       <c r="B104" s="2">
-        <v>610010004651</v>
-      </c>
-      <c r="C104" t="s">
-        <v>32</v>
+        <v>600010000961</v>
+      </c>
+      <c r="C104" s="14" t="s">
+        <v>31</v>
       </c>
       <c r="D104">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E104">
         <v>0</v>
       </c>
       <c r="F104">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G104" t="s">
         <v>151</v>
@@ -4102,19 +4102,19 @@
         <v>30</v>
       </c>
       <c r="B105" s="2">
-        <v>600010000962</v>
+        <v>610010004651</v>
       </c>
       <c r="C105" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="D105">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E105">
         <v>0</v>
       </c>
       <c r="F105">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G105" t="s">
         <v>151</v>
@@ -4125,19 +4125,19 @@
         <v>30</v>
       </c>
       <c r="B106" s="2">
-        <v>610010003151</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>51</v>
+        <v>600010000962</v>
+      </c>
+      <c r="C106" t="s">
+        <v>100</v>
       </c>
       <c r="D106">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E106">
         <v>0</v>
       </c>
       <c r="F106">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G106" t="s">
         <v>151</v>
@@ -4148,19 +4148,19 @@
         <v>30</v>
       </c>
       <c r="B107" s="2">
-        <v>610010005863</v>
-      </c>
-      <c r="C107" t="s">
-        <v>101</v>
+        <v>610010003151</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="D107">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E107">
         <v>0</v>
       </c>
       <c r="F107">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G107" t="s">
         <v>151</v>
@@ -4171,19 +4171,19 @@
         <v>30</v>
       </c>
       <c r="B108" s="2">
-        <v>610010002001</v>
+        <v>610010005863</v>
       </c>
       <c r="C108" t="s">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="D108">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E108">
         <v>0</v>
       </c>
       <c r="F108">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G108" t="s">
         <v>151</v>
@@ -4194,19 +4194,19 @@
         <v>30</v>
       </c>
       <c r="B109" s="2">
-        <v>610010004650</v>
+        <v>610010002001</v>
       </c>
       <c r="C109" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D109">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E109">
         <v>0</v>
       </c>
       <c r="F109">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G109" t="s">
         <v>151</v>
@@ -4217,10 +4217,10 @@
         <v>30</v>
       </c>
       <c r="B110" s="2">
-        <v>610010005864</v>
-      </c>
-      <c r="C110" s="14" t="s">
-        <v>102</v>
+        <v>610010004650</v>
+      </c>
+      <c r="C110" t="s">
+        <v>34</v>
       </c>
       <c r="D110">
         <v>4</v>
@@ -4240,19 +4240,19 @@
         <v>30</v>
       </c>
       <c r="B111" s="2">
-        <v>610010002206</v>
+        <v>610010005864</v>
       </c>
       <c r="C111" s="14" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="D111">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E111">
         <v>0</v>
       </c>
       <c r="F111">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G111" t="s">
         <v>151</v>
@@ -4263,10 +4263,10 @@
         <v>30</v>
       </c>
       <c r="B112" s="2">
-        <v>610010002317</v>
+        <v>610010002206</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D112">
         <v>7</v>
@@ -4286,19 +4286,19 @@
         <v>30</v>
       </c>
       <c r="B113" s="2">
-        <v>610010004653</v>
+        <v>610010002317</v>
       </c>
       <c r="C113" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D113">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E113">
         <v>0</v>
       </c>
       <c r="F113">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G113" t="s">
         <v>151</v>
@@ -4309,19 +4309,19 @@
         <v>30</v>
       </c>
       <c r="B114" s="2">
-        <v>610010005509</v>
+        <v>610010004653</v>
       </c>
       <c r="C114" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D114">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E114">
         <v>0</v>
       </c>
       <c r="F114">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G114" t="s">
         <v>151</v>
@@ -4332,19 +4332,19 @@
         <v>30</v>
       </c>
       <c r="B115" s="2">
-        <v>610010005527</v>
-      </c>
-      <c r="C115" t="s">
-        <v>103</v>
+        <v>610010005509</v>
+      </c>
+      <c r="C115" s="14" t="s">
+        <v>38</v>
       </c>
       <c r="D115">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E115">
         <v>0</v>
       </c>
       <c r="F115">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G115" t="s">
         <v>151</v>
@@ -4355,19 +4355,19 @@
         <v>30</v>
       </c>
       <c r="B116" s="2">
-        <v>610010002221</v>
+        <v>610010005527</v>
       </c>
       <c r="C116" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D116">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E116">
         <v>0</v>
       </c>
       <c r="F116">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G116" t="s">
         <v>151</v>
@@ -4378,10 +4378,10 @@
         <v>30</v>
       </c>
       <c r="B117" s="2">
-        <v>610010002315</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>105</v>
+        <v>610010002221</v>
+      </c>
+      <c r="C117" t="s">
+        <v>104</v>
       </c>
       <c r="D117">
         <v>7</v>
@@ -4401,19 +4401,19 @@
         <v>30</v>
       </c>
       <c r="B118" s="2">
-        <v>610010005660</v>
-      </c>
-      <c r="C118" t="s">
-        <v>106</v>
+        <v>610010002315</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="D118">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E118">
         <v>0</v>
       </c>
       <c r="F118">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G118" t="s">
         <v>151</v>
@@ -4424,10 +4424,10 @@
         <v>30</v>
       </c>
       <c r="B119" s="2">
-        <v>610010005788</v>
+        <v>610010005660</v>
       </c>
       <c r="C119" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D119">
         <v>4</v>
@@ -4447,10 +4447,10 @@
         <v>30</v>
       </c>
       <c r="B120" s="2">
-        <v>610010005661</v>
+        <v>610010005788</v>
       </c>
       <c r="C120" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D120">
         <v>4</v>
@@ -4470,19 +4470,19 @@
         <v>30</v>
       </c>
       <c r="B121" s="2">
-        <v>610010002220</v>
-      </c>
-      <c r="C121" s="14" t="s">
-        <v>39</v>
+        <v>610010005661</v>
+      </c>
+      <c r="C121" t="s">
+        <v>108</v>
       </c>
       <c r="D121">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E121">
         <v>0</v>
       </c>
       <c r="F121">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G121" t="s">
         <v>151</v>
@@ -4493,19 +4493,19 @@
         <v>30</v>
       </c>
       <c r="B122" s="2">
-        <v>610010004652</v>
+        <v>610010002220</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D122">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E122">
         <v>0</v>
       </c>
       <c r="F122">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G122" t="s">
         <v>151</v>
@@ -4516,19 +4516,19 @@
         <v>30</v>
       </c>
       <c r="B123" s="2">
-        <v>600010000959</v>
+        <v>610010004652</v>
       </c>
       <c r="C123" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D123">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E123">
         <v>0</v>
       </c>
       <c r="F123">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G123" t="s">
         <v>151</v>
@@ -4539,19 +4539,19 @@
         <v>30</v>
       </c>
       <c r="B124" s="2">
-        <v>610010005866</v>
+        <v>600010000959</v>
       </c>
       <c r="C124" s="14" t="s">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="D124">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E124">
         <v>0</v>
       </c>
       <c r="F124">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G124" t="s">
         <v>151</v>
@@ -4562,10 +4562,10 @@
         <v>30</v>
       </c>
       <c r="B125" s="2">
-        <v>610010005865</v>
+        <v>610010005866</v>
       </c>
       <c r="C125" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D125">
         <v>4</v>
@@ -4585,10 +4585,10 @@
         <v>30</v>
       </c>
       <c r="B126" s="2">
-        <v>610010005526</v>
-      </c>
-      <c r="C126" t="s">
-        <v>111</v>
+        <v>610010005865</v>
+      </c>
+      <c r="C126" s="14" t="s">
+        <v>110</v>
       </c>
       <c r="D126">
         <v>4</v>
@@ -4608,10 +4608,10 @@
         <v>30</v>
       </c>
       <c r="B127" s="2">
-        <v>610010005571</v>
+        <v>610010005526</v>
       </c>
       <c r="C127" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D127">
         <v>4</v>
@@ -4631,10 +4631,10 @@
         <v>30</v>
       </c>
       <c r="B128" s="2">
-        <v>610010005913</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>113</v>
+        <v>610010005571</v>
+      </c>
+      <c r="C128" t="s">
+        <v>112</v>
       </c>
       <c r="D128">
         <v>4</v>
@@ -4654,10 +4654,10 @@
         <v>30</v>
       </c>
       <c r="B129" s="2">
-        <v>610010005912</v>
-      </c>
-      <c r="C129" t="s">
-        <v>114</v>
+        <v>610010005913</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="D129">
         <v>4</v>
@@ -4677,10 +4677,10 @@
         <v>30</v>
       </c>
       <c r="B130" s="2">
-        <v>610010005570</v>
+        <v>610010005912</v>
       </c>
       <c r="C130" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D130">
         <v>4</v>
@@ -4700,10 +4700,10 @@
         <v>30</v>
       </c>
       <c r="B131" s="2">
-        <v>610010005525</v>
+        <v>610010005570</v>
       </c>
       <c r="C131" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D131">
         <v>4</v>
@@ -4720,19 +4720,22 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B132" s="2">
-        <v>610010006068</v>
-      </c>
-      <c r="C132" s="14" t="s">
-        <v>132</v>
+        <v>610010005525</v>
+      </c>
+      <c r="C132" t="s">
+        <v>116</v>
+      </c>
+      <c r="D132">
+        <v>4</v>
       </c>
       <c r="E132">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F132">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G132" t="s">
         <v>151</v>
@@ -4743,10 +4746,10 @@
         <v>29</v>
       </c>
       <c r="B133" s="2">
-        <v>610010006069</v>
+        <v>610010006068</v>
       </c>
       <c r="C133" s="14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E133">
         <v>2</v>
@@ -4763,19 +4766,16 @@
         <v>29</v>
       </c>
       <c r="B134" s="2">
-        <v>610010006070</v>
+        <v>610010006069</v>
       </c>
       <c r="C134" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="D134">
-        <v>5</v>
+        <v>133</v>
       </c>
       <c r="E134">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F134">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G134" t="s">
         <v>151</v>
@@ -4786,16 +4786,16 @@
         <v>29</v>
       </c>
       <c r="B135" s="2">
-        <v>610010005867</v>
+        <v>610010006070</v>
       </c>
       <c r="C135" s="14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D135">
         <v>5</v>
       </c>
       <c r="E135">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F135">
         <v>32</v>
@@ -4809,16 +4809,19 @@
         <v>29</v>
       </c>
       <c r="B136" s="2">
-        <v>610010006054</v>
+        <v>610010005867</v>
       </c>
       <c r="C136" s="14" t="s">
-        <v>136</v>
+        <v>135</v>
+      </c>
+      <c r="D136">
+        <v>5</v>
       </c>
       <c r="E136">
         <v>2</v>
       </c>
       <c r="F136">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G136" t="s">
         <v>151</v>
@@ -4829,19 +4832,16 @@
         <v>29</v>
       </c>
       <c r="B137" s="2">
-        <v>610010006097</v>
-      </c>
-      <c r="C137" t="s">
-        <v>137</v>
-      </c>
-      <c r="D137">
-        <v>5</v>
+        <v>610010006054</v>
+      </c>
+      <c r="C137" s="14" t="s">
+        <v>136</v>
       </c>
       <c r="E137">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F137">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G137" t="s">
         <v>151</v>
@@ -4852,10 +4852,10 @@
         <v>29</v>
       </c>
       <c r="B138" s="2">
-        <v>610010006098</v>
+        <v>610010006097</v>
       </c>
       <c r="C138" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D138">
         <v>5</v>
@@ -4875,16 +4875,16 @@
         <v>29</v>
       </c>
       <c r="B139" s="2">
-        <v>610010006073</v>
-      </c>
-      <c r="C139" s="3" t="s">
-        <v>139</v>
+        <v>610010006098</v>
+      </c>
+      <c r="C139" t="s">
+        <v>138</v>
       </c>
       <c r="D139">
         <v>5</v>
       </c>
       <c r="E139">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F139">
         <v>32</v>
@@ -4898,16 +4898,19 @@
         <v>29</v>
       </c>
       <c r="B140" s="2">
-        <v>610010005960</v>
-      </c>
-      <c r="C140" t="s">
-        <v>140</v>
+        <v>610010006073</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D140">
+        <v>5</v>
       </c>
       <c r="E140">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F140">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G140" t="s">
         <v>151</v>
@@ -4918,19 +4921,16 @@
         <v>29</v>
       </c>
       <c r="B141" s="2">
-        <v>610010004563</v>
+        <v>610010005960</v>
       </c>
       <c r="C141" t="s">
-        <v>141</v>
-      </c>
-      <c r="D141">
-        <v>5</v>
+        <v>140</v>
       </c>
       <c r="E141">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F141">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G141" t="s">
         <v>151</v>
@@ -4941,10 +4941,10 @@
         <v>29</v>
       </c>
       <c r="B142" s="2">
-        <v>610010004560</v>
+        <v>610010004563</v>
       </c>
       <c r="C142" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D142">
         <v>5</v>
@@ -4964,10 +4964,10 @@
         <v>29</v>
       </c>
       <c r="B143" s="2">
-        <v>610010004561</v>
-      </c>
-      <c r="C143" s="14" t="s">
-        <v>143</v>
+        <v>610010004560</v>
+      </c>
+      <c r="C143" t="s">
+        <v>142</v>
       </c>
       <c r="D143">
         <v>5</v>
@@ -4987,10 +4987,10 @@
         <v>29</v>
       </c>
       <c r="B144" s="2">
-        <v>610010004562</v>
+        <v>610010004561</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D144">
         <v>5</v>
@@ -5010,16 +5010,16 @@
         <v>29</v>
       </c>
       <c r="B145" s="2">
-        <v>610010006072</v>
+        <v>610010004562</v>
       </c>
       <c r="C145" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D145">
         <v>5</v>
       </c>
       <c r="E145">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F145">
         <v>32</v>
@@ -5033,19 +5033,22 @@
         <v>29</v>
       </c>
       <c r="B146" s="2">
-        <v>600010000897</v>
-      </c>
-      <c r="C146" t="s">
-        <v>146</v>
+        <v>610010006072</v>
+      </c>
+      <c r="C146" s="14" t="s">
+        <v>145</v>
       </c>
       <c r="D146">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="E146">
+        <v>8</v>
       </c>
       <c r="F146">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G146" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
@@ -5053,10 +5056,10 @@
         <v>29</v>
       </c>
       <c r="B147" s="2">
-        <v>600010009350</v>
+        <v>600010000897</v>
       </c>
       <c r="C147" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D147">
         <v>6</v>
@@ -5073,10 +5076,10 @@
         <v>29</v>
       </c>
       <c r="B148" s="2">
-        <v>600010009351</v>
+        <v>600010009350</v>
       </c>
       <c r="C148" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D148">
         <v>6</v>
@@ -5093,22 +5096,19 @@
         <v>29</v>
       </c>
       <c r="B149" s="2">
-        <v>610010006071</v>
+        <v>600010009351</v>
       </c>
       <c r="C149" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D149">
-        <v>5</v>
-      </c>
-      <c r="E149">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F149">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G149" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
@@ -5116,16 +5116,19 @@
         <v>29</v>
       </c>
       <c r="B150" s="2">
-        <v>610010006101</v>
+        <v>610010006071</v>
       </c>
       <c r="C150" t="s">
-        <v>153</v>
+        <v>152</v>
+      </c>
+      <c r="D150">
+        <v>5</v>
       </c>
       <c r="E150">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F150">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G150" t="s">
         <v>151</v>
@@ -5136,19 +5139,16 @@
         <v>29</v>
       </c>
       <c r="B151" s="2">
-        <v>610010005779</v>
+        <v>610010006101</v>
       </c>
       <c r="C151" t="s">
-        <v>154</v>
-      </c>
-      <c r="D151">
-        <v>5</v>
+        <v>153</v>
       </c>
       <c r="E151">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F151">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G151" t="s">
         <v>151</v>
@@ -5159,10 +5159,10 @@
         <v>29</v>
       </c>
       <c r="B152" s="2">
-        <v>610010005781</v>
+        <v>610010005779</v>
       </c>
       <c r="C152" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D152">
         <v>5</v>
@@ -5182,19 +5182,19 @@
         <v>29</v>
       </c>
       <c r="B153" s="2">
-        <v>610110001491</v>
+        <v>610010005781</v>
       </c>
       <c r="C153" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D153">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E153">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F153">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G153" t="s">
         <v>151</v>
@@ -5205,19 +5205,19 @@
         <v>29</v>
       </c>
       <c r="B154" s="2">
-        <v>610010005273</v>
+        <v>610110001491</v>
       </c>
       <c r="C154" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D154">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E154">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F154">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G154" t="s">
         <v>151</v>
@@ -5228,10 +5228,10 @@
         <v>29</v>
       </c>
       <c r="B155" s="2">
-        <v>610010005276</v>
+        <v>610010005273</v>
       </c>
       <c r="C155" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D155">
         <v>5</v>
@@ -5251,10 +5251,10 @@
         <v>29</v>
       </c>
       <c r="B156" s="2">
-        <v>610010005277</v>
+        <v>610010005276</v>
       </c>
       <c r="C156" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D156">
         <v>5</v>
@@ -5274,10 +5274,10 @@
         <v>29</v>
       </c>
       <c r="B157" s="2">
-        <v>610010005269</v>
+        <v>610010005277</v>
       </c>
       <c r="C157" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D157">
         <v>5</v>
@@ -5297,10 +5297,10 @@
         <v>29</v>
       </c>
       <c r="B158" s="2">
-        <v>610010005267</v>
+        <v>610010005269</v>
       </c>
       <c r="C158" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D158">
         <v>5</v>
@@ -5320,19 +5320,19 @@
         <v>29</v>
       </c>
       <c r="B159" s="2">
-        <v>610110000995</v>
+        <v>610010005267</v>
       </c>
       <c r="C159" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D159">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E159">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F159">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G159" t="s">
         <v>151</v>
@@ -5343,10 +5343,10 @@
         <v>29</v>
       </c>
       <c r="B160" s="2">
-        <v>610110001007</v>
+        <v>610110000995</v>
       </c>
       <c r="C160" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D160">
         <v>7</v>
@@ -5366,10 +5366,10 @@
         <v>29</v>
       </c>
       <c r="B161" s="2">
-        <v>610110001008</v>
+        <v>610110001007</v>
       </c>
       <c r="C161" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D161">
         <v>7</v>
@@ -5386,22 +5386,22 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B162" s="2">
-        <v>610010005930</v>
+        <v>610110001008</v>
       </c>
       <c r="C162" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D162">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E162">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F162">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="G162" t="s">
         <v>151</v>
@@ -5412,10 +5412,10 @@
         <v>30</v>
       </c>
       <c r="B163" s="2">
-        <v>610010005931</v>
+        <v>610010005930</v>
       </c>
       <c r="C163" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D163">
         <v>4</v>
@@ -5435,10 +5435,10 @@
         <v>30</v>
       </c>
       <c r="B164" s="2">
-        <v>610010006327</v>
+        <v>610010005931</v>
       </c>
       <c r="C164" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D164">
         <v>4</v>
@@ -5455,22 +5455,22 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B165" s="2">
-        <v>610010005598</v>
+        <v>610010006327</v>
       </c>
       <c r="C165" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D165">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E165">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F165">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G165" t="s">
         <v>151</v>
@@ -5481,10 +5481,10 @@
         <v>29</v>
       </c>
       <c r="B166" s="2">
-        <v>610010005600</v>
+        <v>610010005598</v>
       </c>
       <c r="C166" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D166">
         <v>5</v>
@@ -5504,10 +5504,10 @@
         <v>29</v>
       </c>
       <c r="B167" s="2">
-        <v>610010005599</v>
+        <v>610010005600</v>
       </c>
       <c r="C167" t="s">
-        <v>218</v>
+        <v>170</v>
       </c>
       <c r="D167">
         <v>5</v>
@@ -5527,10 +5527,10 @@
         <v>29</v>
       </c>
       <c r="B168" s="2">
-        <v>610010005601</v>
+        <v>610010005599</v>
       </c>
       <c r="C168" t="s">
-        <v>171</v>
+        <v>218</v>
       </c>
       <c r="D168">
         <v>5</v>
@@ -5550,10 +5550,10 @@
         <v>29</v>
       </c>
       <c r="B169" s="2">
-        <v>610010005656</v>
+        <v>610010005601</v>
       </c>
       <c r="C169" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D169">
         <v>5</v>
@@ -5573,10 +5573,10 @@
         <v>29</v>
       </c>
       <c r="B170" s="2">
-        <v>610010005658</v>
+        <v>610010005656</v>
       </c>
       <c r="C170" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D170">
         <v>5</v>
@@ -5596,10 +5596,10 @@
         <v>29</v>
       </c>
       <c r="B171" s="2">
-        <v>610010005657</v>
+        <v>610010005658</v>
       </c>
       <c r="C171" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D171">
         <v>5</v>
@@ -5619,10 +5619,10 @@
         <v>29</v>
       </c>
       <c r="B172" s="2">
-        <v>610010005659</v>
+        <v>610010005657</v>
       </c>
       <c r="C172" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D172">
         <v>5</v>
@@ -5642,10 +5642,10 @@
         <v>29</v>
       </c>
       <c r="B173" s="2">
-        <v>610010004674</v>
+        <v>610010005659</v>
       </c>
       <c r="C173" t="s">
-        <v>224</v>
+        <v>171</v>
       </c>
       <c r="D173">
         <v>5</v>
@@ -5665,10 +5665,10 @@
         <v>29</v>
       </c>
       <c r="B174" s="2">
-        <v>610010002255</v>
+        <v>610010004674</v>
       </c>
       <c r="C174" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D174">
         <v>5</v>
@@ -5688,10 +5688,10 @@
         <v>29</v>
       </c>
       <c r="B175" s="2">
-        <v>610010004677</v>
+        <v>610010002255</v>
       </c>
       <c r="C175" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D175">
         <v>5</v>
@@ -5711,10 +5711,10 @@
         <v>29</v>
       </c>
       <c r="B176" s="2">
-        <v>610010004676</v>
+        <v>610010004677</v>
       </c>
       <c r="C176" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D176">
         <v>5</v>
@@ -5734,10 +5734,10 @@
         <v>29</v>
       </c>
       <c r="B177" s="2">
-        <v>610010004673</v>
+        <v>610010004676</v>
       </c>
       <c r="C177" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D177">
         <v>5</v>
@@ -5757,10 +5757,10 @@
         <v>29</v>
       </c>
       <c r="B178" s="2">
-        <v>610010002258</v>
+        <v>610010004673</v>
       </c>
       <c r="C178" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D178">
         <v>5</v>
@@ -5780,10 +5780,10 @@
         <v>29</v>
       </c>
       <c r="B179" s="2">
-        <v>610010002256</v>
+        <v>610010002258</v>
       </c>
       <c r="C179" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D179">
         <v>5</v>
@@ -5803,10 +5803,10 @@
         <v>29</v>
       </c>
       <c r="B180" s="2">
-        <v>610010002254</v>
+        <v>610010002256</v>
       </c>
       <c r="C180" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D180">
         <v>5</v>
@@ -5826,10 +5826,10 @@
         <v>29</v>
       </c>
       <c r="B181" s="2">
-        <v>610010004675</v>
+        <v>610010002254</v>
       </c>
       <c r="C181" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D181">
         <v>5</v>
@@ -5849,10 +5849,10 @@
         <v>29</v>
       </c>
       <c r="B182" s="2">
-        <v>610010002257</v>
+        <v>610010004675</v>
       </c>
       <c r="C182" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D182">
         <v>5</v>
@@ -5872,10 +5872,10 @@
         <v>29</v>
       </c>
       <c r="B183" s="2">
-        <v>610010005776</v>
+        <v>610010002257</v>
       </c>
       <c r="C183" t="s">
-        <v>173</v>
+        <v>233</v>
       </c>
       <c r="D183">
         <v>5</v>
@@ -5895,10 +5895,10 @@
         <v>29</v>
       </c>
       <c r="B184" s="2">
-        <v>610010005773</v>
+        <v>610010005776</v>
       </c>
       <c r="C184" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D184">
         <v>5</v>
@@ -5918,10 +5918,10 @@
         <v>29</v>
       </c>
       <c r="B185" s="2">
-        <v>610010005774</v>
+        <v>610010005773</v>
       </c>
       <c r="C185" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D185">
         <v>5</v>
@@ -5941,10 +5941,10 @@
         <v>29</v>
       </c>
       <c r="B186" s="2">
-        <v>610010005772</v>
+        <v>610010005774</v>
       </c>
       <c r="C186" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D186">
         <v>5</v>
@@ -5964,10 +5964,10 @@
         <v>29</v>
       </c>
       <c r="B187" s="2">
-        <v>610010005775</v>
+        <v>610010005772</v>
       </c>
       <c r="C187" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D187">
         <v>5</v>
@@ -5987,10 +5987,10 @@
         <v>29</v>
       </c>
       <c r="B188" s="2">
-        <v>610010005771</v>
+        <v>610010005775</v>
       </c>
       <c r="C188" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D188">
         <v>5</v>
@@ -6010,19 +6010,19 @@
         <v>29</v>
       </c>
       <c r="B189" s="2">
-        <v>610010005878</v>
+        <v>610010005771</v>
       </c>
       <c r="C189" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D189">
         <v>5</v>
       </c>
       <c r="E189">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F189">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G189" t="s">
         <v>151</v>
@@ -6033,10 +6033,10 @@
         <v>29</v>
       </c>
       <c r="B190" s="2">
-        <v>610010005875</v>
+        <v>610010005878</v>
       </c>
       <c r="C190" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D190">
         <v>5</v>
@@ -6056,10 +6056,10 @@
         <v>29</v>
       </c>
       <c r="B191" s="2">
-        <v>610010005876</v>
+        <v>610010005875</v>
       </c>
       <c r="C191" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D191">
         <v>5</v>
@@ -6079,10 +6079,10 @@
         <v>29</v>
       </c>
       <c r="B192" s="2">
-        <v>610010005874</v>
+        <v>610010005876</v>
       </c>
       <c r="C192" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D192">
         <v>5</v>
@@ -6102,10 +6102,10 @@
         <v>29</v>
       </c>
       <c r="B193" s="2">
-        <v>610010005877</v>
+        <v>610010005874</v>
       </c>
       <c r="C193" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D193">
         <v>5</v>
@@ -6125,10 +6125,10 @@
         <v>29</v>
       </c>
       <c r="B194" s="2">
-        <v>610010005873</v>
+        <v>610010005877</v>
       </c>
       <c r="C194" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D194">
         <v>5</v>
@@ -6148,19 +6148,19 @@
         <v>29</v>
       </c>
       <c r="B195" s="2">
-        <v>610010005593</v>
+        <v>610010005873</v>
       </c>
       <c r="C195" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D195">
         <v>5</v>
       </c>
       <c r="E195">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F195">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G195" t="s">
         <v>151</v>
@@ -6171,10 +6171,10 @@
         <v>29</v>
       </c>
       <c r="B196" s="2">
-        <v>610010005597</v>
+        <v>610010005593</v>
       </c>
       <c r="C196" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D196">
         <v>5</v>
@@ -6194,10 +6194,10 @@
         <v>29</v>
       </c>
       <c r="B197" s="2">
-        <v>610010005594</v>
+        <v>610010005597</v>
       </c>
       <c r="C197" t="s">
-        <v>234</v>
+        <v>186</v>
       </c>
       <c r="D197">
         <v>5</v>
@@ -6217,10 +6217,10 @@
         <v>29</v>
       </c>
       <c r="B198" s="2">
-        <v>610010005596</v>
+        <v>610010005594</v>
       </c>
       <c r="C198" t="s">
-        <v>187</v>
+        <v>234</v>
       </c>
       <c r="D198">
         <v>5</v>
@@ -6240,10 +6240,10 @@
         <v>29</v>
       </c>
       <c r="B199" s="2">
-        <v>610010005595</v>
+        <v>610010005596</v>
       </c>
       <c r="C199" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D199">
         <v>5</v>
@@ -6263,10 +6263,10 @@
         <v>29</v>
       </c>
       <c r="B200" s="2">
-        <v>610010005649</v>
+        <v>610010005595</v>
       </c>
       <c r="C200" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D200">
         <v>5</v>
@@ -6286,10 +6286,10 @@
         <v>29</v>
       </c>
       <c r="B201" s="2">
-        <v>610010005648</v>
+        <v>610010005649</v>
       </c>
       <c r="C201" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D201">
         <v>5</v>
@@ -6309,10 +6309,10 @@
         <v>29</v>
       </c>
       <c r="B202" s="2">
-        <v>610010005647</v>
+        <v>610010005648</v>
       </c>
       <c r="C202" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D202">
         <v>5</v>
@@ -6332,19 +6332,19 @@
         <v>29</v>
       </c>
       <c r="B203" s="2">
-        <v>610010005584</v>
+        <v>610010005647</v>
       </c>
       <c r="C203" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D203">
         <v>5</v>
       </c>
       <c r="E203">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F203">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G203" t="s">
         <v>151</v>
@@ -6355,10 +6355,10 @@
         <v>29</v>
       </c>
       <c r="B204" s="2">
-        <v>610010005585</v>
+        <v>610010005584</v>
       </c>
       <c r="C204" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D204">
         <v>5</v>
@@ -6378,10 +6378,10 @@
         <v>29</v>
       </c>
       <c r="B205" s="2">
-        <v>610010005586</v>
+        <v>610010005585</v>
       </c>
       <c r="C205" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D205">
         <v>5</v>
@@ -6401,10 +6401,10 @@
         <v>29</v>
       </c>
       <c r="B206" s="2">
-        <v>610010005583</v>
+        <v>610010005586</v>
       </c>
       <c r="C206" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D206">
         <v>5</v>
@@ -6424,10 +6424,10 @@
         <v>29</v>
       </c>
       <c r="B207" s="2">
-        <v>610010005582</v>
+        <v>610010005583</v>
       </c>
       <c r="C207" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D207">
         <v>5</v>
@@ -6447,10 +6447,10 @@
         <v>29</v>
       </c>
       <c r="B208" s="2">
-        <v>610010005581</v>
+        <v>610010005582</v>
       </c>
       <c r="C208" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D208">
         <v>5</v>
@@ -6470,10 +6470,10 @@
         <v>29</v>
       </c>
       <c r="B209" s="2">
-        <v>610010005653</v>
+        <v>610010005581</v>
       </c>
       <c r="C209" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D209">
         <v>5</v>
@@ -6482,7 +6482,7 @@
         <v>6</v>
       </c>
       <c r="F209">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G209" t="s">
         <v>151</v>
@@ -6493,10 +6493,10 @@
         <v>29</v>
       </c>
       <c r="B210" s="2">
-        <v>610010005654</v>
+        <v>610010005653</v>
       </c>
       <c r="C210" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D210">
         <v>5</v>
@@ -6516,10 +6516,10 @@
         <v>29</v>
       </c>
       <c r="B211" s="2">
-        <v>610010005655</v>
+        <v>610010005654</v>
       </c>
       <c r="C211" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D211">
         <v>5</v>
@@ -6539,10 +6539,10 @@
         <v>29</v>
       </c>
       <c r="B212" s="2">
-        <v>610010005652</v>
+        <v>610010005655</v>
       </c>
       <c r="C212" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D212">
         <v>5</v>
@@ -6562,10 +6562,10 @@
         <v>29</v>
       </c>
       <c r="B213" s="2">
-        <v>610010005651</v>
+        <v>610010005652</v>
       </c>
       <c r="C213" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D213">
         <v>5</v>
@@ -6585,10 +6585,10 @@
         <v>29</v>
       </c>
       <c r="B214" s="2">
-        <v>610010005650</v>
+        <v>610010005651</v>
       </c>
       <c r="C214" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D214">
         <v>5</v>
@@ -6608,10 +6608,10 @@
         <v>29</v>
       </c>
       <c r="B215" s="2">
-        <v>610010005644</v>
+        <v>610010005650</v>
       </c>
       <c r="C215" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D215">
         <v>5</v>
@@ -6631,10 +6631,10 @@
         <v>29</v>
       </c>
       <c r="B216" s="2">
-        <v>610010005645</v>
+        <v>610010005644</v>
       </c>
       <c r="C216" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D216">
         <v>5</v>
@@ -6654,10 +6654,10 @@
         <v>29</v>
       </c>
       <c r="B217" s="2">
-        <v>610010005646</v>
+        <v>610010005645</v>
       </c>
       <c r="C217" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D217">
         <v>5</v>
@@ -6677,10 +6677,10 @@
         <v>29</v>
       </c>
       <c r="B218" s="2">
-        <v>610010005643</v>
+        <v>610010005646</v>
       </c>
       <c r="C218" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D218">
         <v>5</v>
@@ -6700,10 +6700,10 @@
         <v>29</v>
       </c>
       <c r="B219" s="2">
-        <v>610010005642</v>
+        <v>610010005643</v>
       </c>
       <c r="C219" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D219">
         <v>5</v>
@@ -6723,10 +6723,10 @@
         <v>29</v>
       </c>
       <c r="B220" s="2">
-        <v>610010005641</v>
+        <v>610010005642</v>
       </c>
       <c r="C220" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D220">
         <v>5</v>
@@ -6746,19 +6746,19 @@
         <v>29</v>
       </c>
       <c r="B221" s="2">
-        <v>600010000900</v>
+        <v>610010005641</v>
       </c>
       <c r="C221" t="s">
-        <v>235</v>
+        <v>197</v>
       </c>
       <c r="D221">
         <v>5</v>
       </c>
       <c r="E221">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F221">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G221" t="s">
         <v>151</v>
@@ -6769,19 +6769,19 @@
         <v>29</v>
       </c>
       <c r="B222" s="2">
-        <v>610010003037</v>
+        <v>600010000900</v>
       </c>
       <c r="C222" t="s">
-        <v>198</v>
+        <v>235</v>
       </c>
       <c r="D222">
         <v>5</v>
       </c>
       <c r="E222">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F222">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G222" t="s">
         <v>151</v>
@@ -6792,19 +6792,19 @@
         <v>29</v>
       </c>
       <c r="B223" s="2">
-        <v>610010003033</v>
+        <v>610010003037</v>
       </c>
       <c r="C223" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D223">
         <v>5</v>
       </c>
       <c r="E223">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F223">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G223" t="s">
         <v>151</v>
@@ -6815,19 +6815,19 @@
         <v>29</v>
       </c>
       <c r="B224" s="2">
-        <v>610010003036</v>
+        <v>610010003033</v>
       </c>
       <c r="C224" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D224">
         <v>5</v>
       </c>
       <c r="E224">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F224">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G224" t="s">
         <v>151</v>
@@ -6838,19 +6838,19 @@
         <v>29</v>
       </c>
       <c r="B225" s="2">
-        <v>600010000901</v>
+        <v>610010003036</v>
       </c>
       <c r="C225" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="D225">
         <v>5</v>
       </c>
       <c r="E225">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F225">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G225" t="s">
         <v>151</v>
@@ -6861,10 +6861,10 @@
         <v>29</v>
       </c>
       <c r="B226" s="2">
-        <v>610010004519</v>
+        <v>600010000901</v>
       </c>
       <c r="C226" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D226">
         <v>5</v>
@@ -6884,10 +6884,10 @@
         <v>29</v>
       </c>
       <c r="B227" s="2">
-        <v>610010004520</v>
+        <v>610010004519</v>
       </c>
       <c r="C227" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D227">
         <v>5</v>
@@ -6907,10 +6907,10 @@
         <v>29</v>
       </c>
       <c r="B228" s="2">
-        <v>610010004521</v>
+        <v>610010004520</v>
       </c>
       <c r="C228" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D228">
         <v>5</v>
@@ -6930,10 +6930,10 @@
         <v>29</v>
       </c>
       <c r="B229" s="2">
-        <v>610010004522</v>
+        <v>610010004521</v>
       </c>
       <c r="C229" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D229">
         <v>5</v>
@@ -6953,10 +6953,10 @@
         <v>29</v>
       </c>
       <c r="B230" s="2">
-        <v>610010004686</v>
+        <v>610010004522</v>
       </c>
       <c r="C230" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D230">
         <v>5</v>
@@ -6976,10 +6976,10 @@
         <v>29</v>
       </c>
       <c r="B231" s="2">
-        <v>610010004685</v>
+        <v>610010004686</v>
       </c>
       <c r="C231" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D231">
         <v>5</v>
@@ -6999,10 +6999,10 @@
         <v>29</v>
       </c>
       <c r="B232" s="2">
-        <v>610010004683</v>
+        <v>610010004685</v>
       </c>
       <c r="C232" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D232">
         <v>5</v>
@@ -7022,10 +7022,10 @@
         <v>29</v>
       </c>
       <c r="B233" s="2">
-        <v>610010004684</v>
+        <v>610010004683</v>
       </c>
       <c r="C233" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D233">
         <v>5</v>
@@ -7045,10 +7045,10 @@
         <v>29</v>
       </c>
       <c r="B234" s="2">
-        <v>610010004687</v>
+        <v>610010004684</v>
       </c>
       <c r="C234" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D234">
         <v>5</v>
@@ -7068,19 +7068,19 @@
         <v>29</v>
       </c>
       <c r="B235" s="2">
-        <v>610010005859</v>
+        <v>610010004687</v>
       </c>
       <c r="C235" t="s">
-        <v>201</v>
+        <v>245</v>
       </c>
       <c r="D235">
         <v>5</v>
       </c>
       <c r="E235">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F235">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G235" t="s">
         <v>151</v>
@@ -7091,19 +7091,19 @@
         <v>29</v>
       </c>
       <c r="B236" s="2">
-        <v>610010005782</v>
+        <v>610010005859</v>
       </c>
       <c r="C236" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D236">
         <v>5</v>
       </c>
       <c r="E236">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F236">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G236" t="s">
         <v>151</v>
@@ -7114,19 +7114,19 @@
         <v>29</v>
       </c>
       <c r="B237" s="2">
-        <v>610010005862</v>
+        <v>610010005782</v>
       </c>
       <c r="C237" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D237">
         <v>5</v>
       </c>
       <c r="E237">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F237">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G237" t="s">
         <v>151</v>
@@ -7137,19 +7137,19 @@
         <v>29</v>
       </c>
       <c r="B238" s="2">
-        <v>610010005780</v>
+        <v>610010005862</v>
       </c>
       <c r="C238" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D238">
         <v>5</v>
       </c>
       <c r="E238">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F238">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G238" t="s">
         <v>151</v>
@@ -7160,19 +7160,19 @@
         <v>29</v>
       </c>
       <c r="B239" s="2">
-        <v>610010005860</v>
+        <v>610010005780</v>
       </c>
       <c r="C239" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D239">
         <v>5</v>
       </c>
       <c r="E239">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F239">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G239" t="s">
         <v>151</v>
@@ -7183,19 +7183,19 @@
         <v>29</v>
       </c>
       <c r="B240" s="2">
-        <v>610010005778</v>
+        <v>610010005860</v>
       </c>
       <c r="C240" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D240">
         <v>5</v>
       </c>
       <c r="E240">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F240">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G240" t="s">
         <v>151</v>
@@ -7206,19 +7206,19 @@
         <v>29</v>
       </c>
       <c r="B241" s="2">
-        <v>610010005858</v>
+        <v>610010005778</v>
       </c>
       <c r="C241" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D241">
         <v>5</v>
       </c>
       <c r="E241">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F241">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G241" t="s">
         <v>151</v>
@@ -7229,16 +7229,16 @@
         <v>29</v>
       </c>
       <c r="B242" s="2">
-        <v>610010005871</v>
+        <v>610010005858</v>
       </c>
       <c r="C242" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="D242">
         <v>5</v>
       </c>
       <c r="E242">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F242">
         <v>35</v>
@@ -7252,10 +7252,10 @@
         <v>29</v>
       </c>
       <c r="B243" s="2">
-        <v>610010005869</v>
+        <v>610010005871</v>
       </c>
       <c r="C243" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D243">
         <v>5</v>
@@ -7264,7 +7264,7 @@
         <v>7</v>
       </c>
       <c r="F243">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G243" t="s">
         <v>151</v>
@@ -7275,10 +7275,10 @@
         <v>29</v>
       </c>
       <c r="B244" s="2">
-        <v>610010005872</v>
+        <v>610010005869</v>
       </c>
       <c r="C244" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D244">
         <v>5</v>
@@ -7298,10 +7298,10 @@
         <v>29</v>
       </c>
       <c r="B245" s="2">
-        <v>610010005870</v>
+        <v>610010005872</v>
       </c>
       <c r="C245" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D245">
         <v>5</v>
@@ -7321,10 +7321,10 @@
         <v>29</v>
       </c>
       <c r="B246" s="2">
-        <v>610010005868</v>
+        <v>610010005870</v>
       </c>
       <c r="C246" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D246">
         <v>5</v>
@@ -7344,16 +7344,16 @@
         <v>29</v>
       </c>
       <c r="B247" s="2">
-        <v>610010005861</v>
+        <v>610010005868</v>
       </c>
       <c r="C247" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="D247">
         <v>5</v>
       </c>
       <c r="E247">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F247">
         <v>40</v>
@@ -7367,16 +7367,16 @@
         <v>29</v>
       </c>
       <c r="B248" s="2">
-        <v>610010005857</v>
+        <v>610010005861</v>
       </c>
       <c r="C248" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D248">
         <v>5</v>
       </c>
       <c r="E248">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F248">
         <v>40</v>
@@ -7390,10 +7390,10 @@
         <v>29</v>
       </c>
       <c r="B249" s="2">
-        <v>600010002006</v>
+        <v>610010005857</v>
       </c>
       <c r="C249" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="D249">
         <v>5</v>
@@ -7413,10 +7413,10 @@
         <v>29</v>
       </c>
       <c r="B250" s="2">
-        <v>610010006099</v>
+        <v>600010002006</v>
       </c>
       <c r="C250" t="s">
-        <v>210</v>
+        <v>246</v>
       </c>
       <c r="D250">
         <v>5</v>
@@ -7436,19 +7436,19 @@
         <v>29</v>
       </c>
       <c r="B251" s="2">
-        <v>610010006051</v>
+        <v>610010006099</v>
       </c>
       <c r="C251" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D251">
         <v>5</v>
       </c>
       <c r="E251">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F251">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G251" t="s">
         <v>151</v>
@@ -7459,10 +7459,10 @@
         <v>29</v>
       </c>
       <c r="B252" s="2">
-        <v>610010006052</v>
+        <v>610010006051</v>
       </c>
       <c r="C252" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D252">
         <v>5</v>
@@ -7482,19 +7482,19 @@
         <v>29</v>
       </c>
       <c r="B253" s="2">
-        <v>610010006095</v>
+        <v>610010006052</v>
       </c>
       <c r="C253" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D253">
         <v>5</v>
       </c>
       <c r="E253">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F253">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G253" t="s">
         <v>151</v>
@@ -7505,7 +7505,7 @@
         <v>29</v>
       </c>
       <c r="B254" s="2">
-        <v>610010006037</v>
+        <v>610010006095</v>
       </c>
       <c r="C254" t="s">
         <v>213</v>
@@ -7514,10 +7514,10 @@
         <v>5</v>
       </c>
       <c r="E254">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F254">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G254" t="s">
         <v>151</v>
@@ -7528,19 +7528,19 @@
         <v>29</v>
       </c>
       <c r="B255" s="2">
-        <v>610010005783</v>
+        <v>610010006037</v>
       </c>
       <c r="C255" t="s">
-        <v>247</v>
+        <v>213</v>
       </c>
       <c r="D255">
         <v>5</v>
       </c>
       <c r="E255">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F255">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G255" t="s">
         <v>151</v>
@@ -7551,10 +7551,10 @@
         <v>29</v>
       </c>
       <c r="B256" s="2">
-        <v>610010005785</v>
+        <v>610010005783</v>
       </c>
       <c r="C256" t="s">
-        <v>276</v>
+        <v>247</v>
       </c>
       <c r="D256">
         <v>5</v>
@@ -7574,19 +7574,19 @@
         <v>29</v>
       </c>
       <c r="B257" s="2">
-        <v>610010005784</v>
+        <v>610010005785</v>
       </c>
       <c r="C257" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="D257">
         <v>5</v>
       </c>
       <c r="E257">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F257">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G257" t="s">
         <v>151</v>
@@ -7597,19 +7597,19 @@
         <v>29</v>
       </c>
       <c r="B258" s="2">
-        <v>610010005272</v>
+        <v>610010005784</v>
       </c>
       <c r="C258" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D258">
         <v>5</v>
       </c>
       <c r="E258">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F258">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G258" t="s">
         <v>151</v>
@@ -7620,19 +7620,19 @@
         <v>29</v>
       </c>
       <c r="B259" s="2">
-        <v>600010000952</v>
+        <v>610010005272</v>
       </c>
       <c r="C259" t="s">
-        <v>214</v>
+        <v>251</v>
       </c>
       <c r="D259">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E259">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F259">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="G259" t="s">
         <v>151</v>
@@ -7643,19 +7643,19 @@
         <v>29</v>
       </c>
       <c r="B260" s="2">
-        <v>600010010197</v>
+        <v>600010000952</v>
       </c>
       <c r="C260" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D260">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E260">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F260">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="G260" t="s">
         <v>151</v>
@@ -7666,19 +7666,19 @@
         <v>29</v>
       </c>
       <c r="B261" s="2">
-        <v>610010001901</v>
+        <v>600010010197</v>
       </c>
       <c r="C261" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D261">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E261">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F261">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="G261" t="s">
         <v>151</v>
@@ -7689,19 +7689,19 @@
         <v>29</v>
       </c>
       <c r="B262" s="2">
-        <v>610010001900</v>
+        <v>610010001901</v>
       </c>
       <c r="C262" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D262">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E262">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F262">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="G262" t="s">
         <v>151</v>
@@ -7712,19 +7712,19 @@
         <v>29</v>
       </c>
       <c r="B263" s="2">
-        <v>600110000239</v>
+        <v>610010001900</v>
       </c>
       <c r="C263" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="D263">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E263">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F263">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G263" t="s">
         <v>151</v>
@@ -7735,19 +7735,19 @@
         <v>29</v>
       </c>
       <c r="B264" s="2">
-        <v>610110000595</v>
+        <v>600110000239</v>
       </c>
       <c r="C264" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D264">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E264">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F264">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G264" t="s">
         <v>151</v>
@@ -7758,19 +7758,19 @@
         <v>29</v>
       </c>
       <c r="B265" s="2">
-        <v>610110000591</v>
+        <v>610110000595</v>
       </c>
       <c r="C265" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D265">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E265">
         <v>5</v>
       </c>
       <c r="F265">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G265" t="s">
         <v>151</v>
@@ -7781,19 +7781,19 @@
         <v>29</v>
       </c>
       <c r="B266" s="2">
-        <v>610110000340</v>
+        <v>610110000591</v>
       </c>
       <c r="C266" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D266">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E266">
         <v>5</v>
       </c>
       <c r="F266">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="G266" t="s">
         <v>151</v>
@@ -7804,19 +7804,19 @@
         <v>29</v>
       </c>
       <c r="B267" s="2">
-        <v>610110000594</v>
+        <v>610110000340</v>
       </c>
       <c r="C267" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="D267">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E267">
         <v>5</v>
       </c>
       <c r="F267">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G267" t="s">
         <v>151</v>
@@ -7827,19 +7827,19 @@
         <v>29</v>
       </c>
       <c r="B268" s="2">
-        <v>610110000590</v>
+        <v>610110000594</v>
       </c>
       <c r="C268" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D268">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E268">
         <v>5</v>
       </c>
       <c r="F268">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G268" t="s">
         <v>151</v>
@@ -7850,19 +7850,19 @@
         <v>29</v>
       </c>
       <c r="B269" s="2">
-        <v>600110000240</v>
+        <v>610110000590</v>
       </c>
       <c r="C269" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D269">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E269">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F269">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="G269" t="s">
         <v>151</v>
@@ -7873,16 +7873,16 @@
         <v>29</v>
       </c>
       <c r="B270" s="2">
-        <v>610110000336</v>
+        <v>600110000240</v>
       </c>
       <c r="C270" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D270">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E270">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F270">
         <v>36</v>
@@ -7896,10 +7896,10 @@
         <v>29</v>
       </c>
       <c r="B271" s="2">
-        <v>610110000335</v>
+        <v>610110000336</v>
       </c>
       <c r="C271" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D271">
         <v>8</v>
@@ -7919,19 +7919,19 @@
         <v>29</v>
       </c>
       <c r="B272" s="2">
-        <v>610110000593</v>
+        <v>610110000335</v>
       </c>
       <c r="C272" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D272">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E272">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F272">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G272" t="s">
         <v>151</v>
@@ -7942,16 +7942,16 @@
         <v>29</v>
       </c>
       <c r="B273" s="2">
-        <v>600110000824</v>
+        <v>610110000593</v>
       </c>
       <c r="C273" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D273">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E273">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F273">
         <v>40</v>
@@ -7965,19 +7965,19 @@
         <v>29</v>
       </c>
       <c r="B274" s="2">
-        <v>600110000798</v>
+        <v>600110000824</v>
       </c>
       <c r="C274" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="D274">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E274">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F274">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G274" t="s">
         <v>151</v>
@@ -7988,19 +7988,19 @@
         <v>29</v>
       </c>
       <c r="B275" s="2">
-        <v>600110000823</v>
+        <v>600110000798</v>
       </c>
       <c r="C275" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D275">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E275">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F275">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G275" t="s">
         <v>151</v>
@@ -8011,19 +8011,19 @@
         <v>29</v>
       </c>
       <c r="B276" s="2">
-        <v>610110001004</v>
+        <v>600110000823</v>
       </c>
       <c r="C276" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D276">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E276">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F276">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G276" t="s">
         <v>151</v>
@@ -8034,10 +8034,10 @@
         <v>29</v>
       </c>
       <c r="B277" s="2">
-        <v>610110001006</v>
+        <v>610110001004</v>
       </c>
       <c r="C277" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D277">
         <v>14</v>
@@ -8057,10 +8057,10 @@
         <v>29</v>
       </c>
       <c r="B278" s="2">
-        <v>610110001003</v>
+        <v>610110001006</v>
       </c>
       <c r="C278" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="D278">
         <v>14</v>
@@ -8080,10 +8080,10 @@
         <v>29</v>
       </c>
       <c r="B279" s="2">
-        <v>610110001005</v>
+        <v>610110001003</v>
       </c>
       <c r="C279" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="D279">
         <v>14</v>
@@ -8103,19 +8103,19 @@
         <v>29</v>
       </c>
       <c r="B280" s="2">
-        <v>610110000990</v>
+        <v>610110001005</v>
       </c>
       <c r="C280" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D280">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E280">
         <v>5</v>
       </c>
       <c r="F280">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G280" t="s">
         <v>151</v>
@@ -8126,10 +8126,10 @@
         <v>29</v>
       </c>
       <c r="B281" s="2">
-        <v>610110000996</v>
+        <v>610110000990</v>
       </c>
       <c r="C281" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D281">
         <v>15</v>
@@ -8149,19 +8149,19 @@
         <v>29</v>
       </c>
       <c r="B282" s="2">
-        <v>610110001508</v>
+        <v>610110000996</v>
       </c>
       <c r="C282" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D282">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E282">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F282">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="G282" t="s">
         <v>151</v>
@@ -8172,19 +8172,19 @@
         <v>29</v>
       </c>
       <c r="B283" s="2">
-        <v>610110000994</v>
+        <v>610110001508</v>
       </c>
       <c r="C283" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D283">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E283">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F283">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="G283" t="s">
         <v>151</v>
@@ -8195,10 +8195,10 @@
         <v>29</v>
       </c>
       <c r="B284" s="2">
-        <v>610110000992</v>
+        <v>610110000994</v>
       </c>
       <c r="C284" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D284">
         <v>15</v>
@@ -8218,10 +8218,10 @@
         <v>29</v>
       </c>
       <c r="B285" s="2">
-        <v>610110000991</v>
+        <v>610110000992</v>
       </c>
       <c r="C285" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D285">
         <v>15</v>
@@ -8241,10 +8241,10 @@
         <v>29</v>
       </c>
       <c r="B286" s="2">
-        <v>610110000989</v>
+        <v>610110000991</v>
       </c>
       <c r="C286" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D286">
         <v>15</v>
@@ -8264,10 +8264,10 @@
         <v>29</v>
       </c>
       <c r="B287" s="2">
-        <v>610110000993</v>
+        <v>610110000989</v>
       </c>
       <c r="C287" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D287">
         <v>15</v>
@@ -8287,10 +8287,10 @@
         <v>29</v>
       </c>
       <c r="B288" s="2">
-        <v>610110000988</v>
+        <v>610110000993</v>
       </c>
       <c r="C288" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D288">
         <v>15</v>
@@ -8305,27 +8305,50 @@
         <v>151</v>
       </c>
     </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A289" t="s">
+        <v>29</v>
+      </c>
+      <c r="B289" s="2">
+        <v>610110000988</v>
+      </c>
+      <c r="C289" t="s">
+        <v>274</v>
+      </c>
+      <c r="D289">
+        <v>15</v>
+      </c>
+      <c r="E289">
+        <v>5</v>
+      </c>
+      <c r="F289">
+        <v>60</v>
+      </c>
+      <c r="G289" t="s">
+        <v>151</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F164" xr:uid="{F30446A3-A986-4686-A765-4C12AB9F4FB1}"/>
-  <conditionalFormatting sqref="B2:B145">
+  <autoFilter ref="A1:F165" xr:uid="{F30446A3-A986-4686-A765-4C12AB9F4FB1}"/>
+  <conditionalFormatting sqref="B2:B146">
     <cfRule type="duplicateValues" dxfId="1" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B149:B150 B154:B155 B159:B160 B164">
+  <conditionalFormatting sqref="B150:B151 B155:B156 B160:B161 B165">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="C10" r:id="rId1" xr:uid="{89506ED6-C4FD-47B8-9FD6-878DCA92E9AA}"/>
     <hyperlink ref="C21" r:id="rId2" xr:uid="{7B1ECE4D-B039-4F94-838C-A478D53267E0}"/>
-    <hyperlink ref="C91" r:id="rId3" xr:uid="{DBB2C1A8-C8F2-410F-A78B-A3CD9BB920C8}"/>
-    <hyperlink ref="C103" r:id="rId4" xr:uid="{DD3336F3-63B5-4EA8-91C3-0AEEB13315C2}"/>
-    <hyperlink ref="C111" r:id="rId5" xr:uid="{8BD8BB4A-70AA-4FA9-9A46-A3355CDFBD57}"/>
-    <hyperlink ref="C104" r:id="rId6" xr:uid="{4FEA0A94-1AD0-4B82-ABB9-6EDBB77929EF}"/>
-    <hyperlink ref="C112:C114" r:id="rId7" display="Bluestone Natural Cleft 24x24" xr:uid="{9D1D11EE-261B-43AD-B4EF-C3FA544A4E70}"/>
-    <hyperlink ref="C121" r:id="rId8" xr:uid="{D42B3E22-C339-41A5-BEA6-DF49B989F449}"/>
-    <hyperlink ref="C123" r:id="rId9" xr:uid="{2B8374D8-0246-4EE4-B96B-FFB02E40BDD1}"/>
-    <hyperlink ref="C112" r:id="rId10" xr:uid="{14C18384-D389-4B97-8461-5247EE585E74}"/>
-    <hyperlink ref="C113" r:id="rId11" xr:uid="{9272B80D-012D-439F-9BD1-11D9279BF6BE}"/>
-    <hyperlink ref="C114" r:id="rId12" xr:uid="{382FF713-4781-44B6-B266-152BC4F3E727}"/>
+    <hyperlink ref="C92" r:id="rId3" xr:uid="{DBB2C1A8-C8F2-410F-A78B-A3CD9BB920C8}"/>
+    <hyperlink ref="C104" r:id="rId4" xr:uid="{DD3336F3-63B5-4EA8-91C3-0AEEB13315C2}"/>
+    <hyperlink ref="C112" r:id="rId5" xr:uid="{8BD8BB4A-70AA-4FA9-9A46-A3355CDFBD57}"/>
+    <hyperlink ref="C105" r:id="rId6" xr:uid="{4FEA0A94-1AD0-4B82-ABB9-6EDBB77929EF}"/>
+    <hyperlink ref="C113:C115" r:id="rId7" display="Bluestone Natural Cleft 24x24" xr:uid="{9D1D11EE-261B-43AD-B4EF-C3FA544A4E70}"/>
+    <hyperlink ref="C122" r:id="rId8" xr:uid="{D42B3E22-C339-41A5-BEA6-DF49B989F449}"/>
+    <hyperlink ref="C124" r:id="rId9" xr:uid="{2B8374D8-0246-4EE4-B96B-FFB02E40BDD1}"/>
+    <hyperlink ref="C113" r:id="rId10" xr:uid="{14C18384-D389-4B97-8461-5247EE585E74}"/>
+    <hyperlink ref="C114" r:id="rId11" xr:uid="{9272B80D-012D-439F-9BD1-11D9279BF6BE}"/>
+    <hyperlink ref="C115" r:id="rId12" xr:uid="{382FF713-4781-44B6-B266-152BC4F3E727}"/>
     <hyperlink ref="C11" r:id="rId13" xr:uid="{3F2A552B-E241-4F03-BD67-4202AAA8FE8E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
